--- a/research/traditional_assets/database/data/bahrain/bahrain_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_shipbuilding_marine.xlsx
@@ -1133,43 +1133,43 @@
         <v>6.08374384236453</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>146.103444787981</v>
       </c>
       <c r="G2">
         <v>1.90536277602524</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.10602523659306</v>
       </c>
       <c r="I2">
         <v>0.179708420113062</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>275.7</v>
       </c>
       <c r="L2">
-        <v>372.190453854659</v>
+        <v>368.663909464073</v>
       </c>
       <c r="M2">
         <v>333.19</v>
       </c>
       <c r="N2">
-        <v>369.280453854659</v>
+        <v>369.114909464073</v>
       </c>
       <c r="O2">
         <v>60.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.361</v>
       </c>
       <c r="Q2">
         <v>0.157004918088051</v>
       </c>
       <c r="R2">
-        <v>0.146136658144221</v>
+        <v>0.146181658144221</v>
       </c>
       <c r="S2">
         <v>0.106277188197372</v>
@@ -1191,13 +1191,13 @@
         <v>0.168118283649883</v>
       </c>
       <c r="X2">
-        <v>0.146136658144221</v>
+        <v>0.147150159741638</v>
       </c>
       <c r="Y2">
         <v>1.04775196358251</v>
       </c>
       <c r="Z2">
-        <v>0.859462113536739</v>
+        <v>0.868143549027009</v>
       </c>
       <c r="AA2">
         <v>60.4</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1461366581442214</v>
+        <v>0.1461816581442214</v>
       </c>
       <c r="C2">
-        <v>372.1904538546589</v>
+        <v>368.6639094640732</v>
       </c>
       <c r="D2">
-        <v>369.2804538546589</v>
+        <v>369.1149094640732</v>
       </c>
       <c r="E2">
-        <v>-60.4</v>
+        <v>-57.039</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.361</v>
       </c>
       <c r="G2">
         <v>2.91</v>
@@ -1451,28 +1451,28 @@
         <v>24.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1690583</v>
       </c>
       <c r="N2">
-        <v>24.7</v>
+        <v>24.5309417</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>24.7</v>
+        <v>24.5309417</v>
       </c>
       <c r="Q2">
-        <v>31.7</v>
+        <v>31.5309417</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1461366581442214</v>
+        <v>0.1471501597416378</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8681435490270092</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.1034447879815</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1461816581442214</v>
+        <v>0.1462266581442214</v>
       </c>
       <c r="C3">
-        <v>368.6639094640732</v>
+        <v>365.137513430462</v>
       </c>
       <c r="D3">
-        <v>369.1149094640732</v>
+        <v>368.949513430462</v>
       </c>
       <c r="E3">
-        <v>-57.039</v>
+        <v>-53.678</v>
       </c>
       <c r="F3">
-        <v>3.361</v>
+        <v>6.722</v>
       </c>
       <c r="G3">
         <v>2.91</v>
@@ -1533,28 +1533,28 @@
         <v>24.7</v>
       </c>
       <c r="M3">
-        <v>0.1690583</v>
+        <v>0.3381165999999999</v>
       </c>
       <c r="N3">
-        <v>24.5309417</v>
+        <v>24.3618834</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>24.5309417</v>
+        <v>24.3618834</v>
       </c>
       <c r="Q3">
-        <v>31.5309417</v>
+        <v>31.3618834</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1471501597416378</v>
+        <v>0.1481843450451239</v>
       </c>
       <c r="T3">
-        <v>0.8681435490270092</v>
+        <v>0.8770021566701419</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.1034447879815</v>
+        <v>73.05172239399073</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1462266581442214</v>
+        <v>0.1462716581442214</v>
       </c>
       <c r="C4">
-        <v>365.137513430462</v>
+        <v>361.6112655544835</v>
       </c>
       <c r="D4">
-        <v>368.949513430462</v>
+        <v>368.7842655544835</v>
       </c>
       <c r="E4">
-        <v>-53.678</v>
+        <v>-50.317</v>
       </c>
       <c r="F4">
-        <v>6.722</v>
+        <v>10.083</v>
       </c>
       <c r="G4">
         <v>2.91</v>
@@ -1615,28 +1615,28 @@
         <v>24.7</v>
       </c>
       <c r="M4">
-        <v>0.3381165999999999</v>
+        <v>0.5071748999999999</v>
       </c>
       <c r="N4">
-        <v>24.3618834</v>
+        <v>24.1928251</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>24.3618834</v>
+        <v>24.1928251</v>
       </c>
       <c r="Q4">
-        <v>31.3618834</v>
+        <v>31.1928251</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1481843450451239</v>
+        <v>0.1492398537569293</v>
       </c>
       <c r="T4">
-        <v>0.8770021566701419</v>
+        <v>0.8860434160172567</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.05172239399073</v>
+        <v>48.70114826266049</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1462716581442214</v>
+        <v>0.1463166581442214</v>
       </c>
       <c r="C5">
-        <v>361.6112655544835</v>
+        <v>358.085165637153</v>
       </c>
       <c r="D5">
-        <v>368.7842655544835</v>
+        <v>368.6191656371529</v>
       </c>
       <c r="E5">
-        <v>-50.317</v>
+        <v>-46.956</v>
       </c>
       <c r="F5">
-        <v>10.083</v>
+        <v>13.444</v>
       </c>
       <c r="G5">
         <v>2.91</v>
@@ -1697,28 +1697,28 @@
         <v>24.7</v>
       </c>
       <c r="M5">
-        <v>0.5071748999999999</v>
+        <v>0.6762331999999999</v>
       </c>
       <c r="N5">
-        <v>24.1928251</v>
+        <v>24.0237668</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>24.1928251</v>
+        <v>24.0237668</v>
       </c>
       <c r="Q5">
-        <v>31.1928251</v>
+        <v>31.0237668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1492398537569293</v>
+        <v>0.150317352233564</v>
       </c>
       <c r="T5">
-        <v>0.8860434160172567</v>
+        <v>0.8952730349341033</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.70114826266049</v>
+        <v>36.52586119699536</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1463166581442214</v>
+        <v>0.1463616581442214</v>
       </c>
       <c r="C6">
-        <v>358.085165637153</v>
+        <v>354.559213479842</v>
       </c>
       <c r="D6">
-        <v>368.6191656371529</v>
+        <v>368.454213479842</v>
       </c>
       <c r="E6">
-        <v>-46.956</v>
+        <v>-43.595</v>
       </c>
       <c r="F6">
-        <v>13.444</v>
+        <v>16.805</v>
       </c>
       <c r="G6">
         <v>2.91</v>
@@ -1779,28 +1779,28 @@
         <v>24.7</v>
       </c>
       <c r="M6">
-        <v>0.6762331999999999</v>
+        <v>0.8452915</v>
       </c>
       <c r="N6">
-        <v>24.0237668</v>
+        <v>23.8547085</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>24.0237668</v>
+        <v>23.8547085</v>
       </c>
       <c r="Q6">
-        <v>31.0237668</v>
+        <v>30.8547085</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.150317352233564</v>
+        <v>0.1514175348886541</v>
       </c>
       <c r="T6">
-        <v>0.8952730349341033</v>
+        <v>0.90469696161762</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.52586119699536</v>
+        <v>29.22068895759629</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1463616581442214</v>
+        <v>0.1464066581442214</v>
       </c>
       <c r="C7">
-        <v>354.559213479842</v>
+        <v>351.033408884277</v>
       </c>
       <c r="D7">
-        <v>368.454213479842</v>
+        <v>368.289408884277</v>
       </c>
       <c r="E7">
-        <v>-43.595</v>
+        <v>-40.23399999999999</v>
       </c>
       <c r="F7">
-        <v>16.805</v>
+        <v>20.166</v>
       </c>
       <c r="G7">
         <v>2.91</v>
@@ -1861,28 +1861,28 @@
         <v>24.7</v>
       </c>
       <c r="M7">
-        <v>0.8452915</v>
+        <v>1.0143498</v>
       </c>
       <c r="N7">
-        <v>23.8547085</v>
+        <v>23.6856502</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>23.8547085</v>
+        <v>23.6856502</v>
       </c>
       <c r="Q7">
-        <v>30.8547085</v>
+        <v>30.6856502</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1514175348886541</v>
+        <v>0.1525411256853419</v>
       </c>
       <c r="T7">
-        <v>0.90469696161762</v>
+        <v>0.9143213973795097</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.22068895759629</v>
+        <v>24.35057413133024</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1464066581442214</v>
+        <v>0.1464516581442214</v>
       </c>
       <c r="C8">
-        <v>351.033408884277</v>
+        <v>347.5077516525398</v>
       </c>
       <c r="D8">
-        <v>368.289408884277</v>
+        <v>368.1247516525397</v>
       </c>
       <c r="E8">
-        <v>-40.234</v>
+        <v>-36.873</v>
       </c>
       <c r="F8">
-        <v>20.166</v>
+        <v>23.52699999999999</v>
       </c>
       <c r="G8">
         <v>2.91</v>
@@ -1943,28 +1943,28 @@
         <v>24.7</v>
       </c>
       <c r="M8">
-        <v>1.0143498</v>
+        <v>1.1834081</v>
       </c>
       <c r="N8">
-        <v>23.6856502</v>
+        <v>23.5165919</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>23.6856502</v>
+        <v>23.5165919</v>
       </c>
       <c r="Q8">
-        <v>30.6856502</v>
+        <v>30.5165919</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1525411256853419</v>
+        <v>0.1536888797249693</v>
       </c>
       <c r="T8">
-        <v>0.9143213973795097</v>
+        <v>0.9241528102545581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.35057413133024</v>
+        <v>20.87192068399735</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1464516581442214</v>
+        <v>0.1464966581442214</v>
       </c>
       <c r="C9">
-        <v>347.5077516525398</v>
+        <v>343.9822415870653</v>
       </c>
       <c r="D9">
-        <v>368.1247516525397</v>
+        <v>367.9602415870653</v>
       </c>
       <c r="E9">
-        <v>-36.873</v>
+        <v>-33.512</v>
       </c>
       <c r="F9">
-        <v>23.527</v>
+        <v>26.888</v>
       </c>
       <c r="G9">
         <v>2.91</v>
@@ -2025,28 +2025,28 @@
         <v>24.7</v>
       </c>
       <c r="M9">
-        <v>1.1834081</v>
+        <v>1.3524664</v>
       </c>
       <c r="N9">
-        <v>23.5165919</v>
+        <v>23.3475336</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>23.5165919</v>
+        <v>23.3475336</v>
       </c>
       <c r="Q9">
-        <v>30.5165919</v>
+        <v>30.3475336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1536888797249693</v>
+        <v>0.1548615849393711</v>
       </c>
       <c r="T9">
-        <v>0.9241528102545581</v>
+        <v>0.9341979494964555</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.87192068399735</v>
+        <v>18.26293059849768</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1464966581442214</v>
+        <v>0.1465416581442214</v>
       </c>
       <c r="C10">
-        <v>343.9822415870653</v>
+        <v>340.4568784906418</v>
       </c>
       <c r="D10">
-        <v>367.9602415870653</v>
+        <v>367.7958784906418</v>
       </c>
       <c r="E10">
-        <v>-33.512</v>
+        <v>-30.151</v>
       </c>
       <c r="F10">
-        <v>26.888</v>
+        <v>30.249</v>
       </c>
       <c r="G10">
         <v>2.91</v>
@@ -2107,28 +2107,28 @@
         <v>24.7</v>
       </c>
       <c r="M10">
-        <v>1.3524664</v>
+        <v>1.5215247</v>
       </c>
       <c r="N10">
-        <v>23.3475336</v>
+        <v>23.1784753</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>23.3475336</v>
+        <v>23.1784753</v>
       </c>
       <c r="Q10">
-        <v>30.3475336</v>
+        <v>30.1784753</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1548615849393711</v>
+        <v>0.1560600638947488</v>
       </c>
       <c r="T10">
-        <v>0.9341979494964555</v>
+        <v>0.9444638610293836</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.26293059849768</v>
+        <v>16.2337160875535</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1465416581442214</v>
+        <v>0.1465866581442214</v>
       </c>
       <c r="C11">
-        <v>340.4568784906418</v>
+        <v>336.9316621664096</v>
       </c>
       <c r="D11">
-        <v>367.7958784906418</v>
+        <v>367.6316621664096</v>
       </c>
       <c r="E11">
-        <v>-30.151</v>
+        <v>-26.79000000000001</v>
       </c>
       <c r="F11">
-        <v>30.249</v>
+        <v>33.60999999999999</v>
       </c>
       <c r="G11">
         <v>2.91</v>
@@ -2189,28 +2189,28 @@
         <v>24.7</v>
       </c>
       <c r="M11">
-        <v>1.5215247</v>
+        <v>1.690583</v>
       </c>
       <c r="N11">
-        <v>23.1784753</v>
+        <v>23.009417</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>23.1784753</v>
+        <v>23.009417</v>
       </c>
       <c r="Q11">
-        <v>30.1784753</v>
+        <v>30.009417</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1560600638947488</v>
+        <v>0.1572851757158016</v>
       </c>
       <c r="T11">
-        <v>0.9444638610293836</v>
+        <v>0.9549579039297101</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.2337160875535</v>
+        <v>14.61034447879815</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1465866581442214</v>
+        <v>0.1466316581442214</v>
       </c>
       <c r="C12">
-        <v>336.9316621664096</v>
+        <v>333.4065924178608</v>
       </c>
       <c r="D12">
-        <v>367.6316621664096</v>
+        <v>367.4675924178608</v>
       </c>
       <c r="E12">
-        <v>-26.79</v>
+        <v>-23.429</v>
       </c>
       <c r="F12">
-        <v>33.61</v>
+        <v>36.971</v>
       </c>
       <c r="G12">
         <v>2.91</v>
@@ -2271,28 +2271,28 @@
         <v>24.7</v>
       </c>
       <c r="M12">
-        <v>1.690583</v>
+        <v>1.8596413</v>
       </c>
       <c r="N12">
-        <v>23.009417</v>
+        <v>22.8403587</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>23.009417</v>
+        <v>22.8403587</v>
       </c>
       <c r="Q12">
-        <v>30.009417</v>
+        <v>29.8403587</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1572851757158016</v>
+        <v>0.1585378181395746</v>
       </c>
       <c r="T12">
-        <v>0.9549579039297101</v>
+        <v>0.965687768018808</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.61034447879814</v>
+        <v>13.28213134436195</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1466316581442214</v>
+        <v>0.1468566581442214</v>
       </c>
       <c r="C13">
-        <v>333.4065924178608</v>
+        <v>329.2274354570794</v>
       </c>
       <c r="D13">
-        <v>367.4675924178608</v>
+        <v>366.6494354570793</v>
       </c>
       <c r="E13">
-        <v>-23.429</v>
+        <v>-20.068</v>
       </c>
       <c r="F13">
-        <v>36.971</v>
+        <v>40.33199999999999</v>
       </c>
       <c r="G13">
         <v>2.91</v>
@@ -2353,45 +2353,45 @@
         <v>24.7</v>
       </c>
       <c r="M13">
-        <v>1.8596413</v>
+        <v>2.089197599999999</v>
       </c>
       <c r="N13">
-        <v>22.8403587</v>
+        <v>22.6108024</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>22.8403587</v>
+        <v>22.6108024</v>
       </c>
       <c r="Q13">
-        <v>29.8403587</v>
+        <v>29.6108024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1585378181395746</v>
+        <v>0.1598189297093425</v>
       </c>
       <c r="T13">
-        <v>0.965687768018808</v>
+        <v>0.9766614926553852</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.28213134436195</v>
+        <v>11.8227208378949</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1468566581442214</v>
+        <v>0.1469166581442214</v>
       </c>
       <c r="C14">
-        <v>329.2274354570794</v>
+        <v>325.6488752001329</v>
       </c>
       <c r="D14">
-        <v>366.6494354570793</v>
+        <v>366.4318752001328</v>
       </c>
       <c r="E14">
-        <v>-20.068</v>
+        <v>-16.707</v>
       </c>
       <c r="F14">
-        <v>40.33199999999999</v>
+        <v>43.693</v>
       </c>
       <c r="G14">
         <v>2.91</v>
@@ -2435,28 +2435,28 @@
         <v>24.7</v>
       </c>
       <c r="M14">
-        <v>2.089197599999999</v>
+        <v>2.2632974</v>
       </c>
       <c r="N14">
-        <v>22.6108024</v>
+        <v>22.4367026</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>22.6108024</v>
+        <v>22.4367026</v>
       </c>
       <c r="Q14">
-        <v>29.6108024</v>
+        <v>29.4367026</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1598189297093425</v>
+        <v>0.1611294921197947</v>
       </c>
       <c r="T14">
-        <v>0.9766614926553852</v>
+        <v>0.987887486823838</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.8227208378949</v>
+        <v>10.91328077344144</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1469166581442214</v>
+        <v>0.1469766581442214</v>
       </c>
       <c r="C15">
-        <v>325.6488752001329</v>
+        <v>322.0705729792918</v>
       </c>
       <c r="D15">
-        <v>366.4318752001328</v>
+        <v>366.2145729792918</v>
       </c>
       <c r="E15">
-        <v>-16.707</v>
+        <v>-13.346</v>
       </c>
       <c r="F15">
-        <v>43.693</v>
+        <v>47.054</v>
       </c>
       <c r="G15">
         <v>2.91</v>
@@ -2517,28 +2517,28 @@
         <v>24.7</v>
       </c>
       <c r="M15">
-        <v>2.2632974</v>
+        <v>2.4373972</v>
       </c>
       <c r="N15">
-        <v>22.4367026</v>
+        <v>22.2626028</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>22.4367026</v>
+        <v>22.2626028</v>
       </c>
       <c r="Q15">
-        <v>29.4367026</v>
+        <v>29.2626028</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1611294921197947</v>
+        <v>0.1624705327258388</v>
       </c>
       <c r="T15">
-        <v>0.987887486823838</v>
+        <v>0.9993745506241153</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.91328077344144</v>
+        <v>10.13376071819562</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1469766581442214</v>
+        <v>0.1472916581442214</v>
       </c>
       <c r="C16">
-        <v>322.0705729792918</v>
+        <v>317.5729515800774</v>
       </c>
       <c r="D16">
-        <v>366.2145729792918</v>
+        <v>365.0779515800774</v>
       </c>
       <c r="E16">
-        <v>-13.346</v>
+        <v>-9.984999999999999</v>
       </c>
       <c r="F16">
-        <v>47.054</v>
+        <v>50.415</v>
       </c>
       <c r="G16">
         <v>2.91</v>
@@ -2599,45 +2599,45 @@
         <v>24.7</v>
       </c>
       <c r="M16">
-        <v>2.4373972</v>
+        <v>2.6972025</v>
       </c>
       <c r="N16">
-        <v>22.2626028</v>
+        <v>22.0027975</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>22.2626028</v>
+        <v>22.0027975</v>
       </c>
       <c r="Q16">
-        <v>29.2626028</v>
+        <v>29.0027975</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1624705327258388</v>
+        <v>0.1638431272284958</v>
       </c>
       <c r="T16">
-        <v>0.9993745506241153</v>
+        <v>1.011131898278517</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.13376071819562</v>
+        <v>9.15763647705354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1472916581442214</v>
+        <v>0.1473686581442214</v>
       </c>
       <c r="C17">
-        <v>317.5729515800774</v>
+        <v>313.9351831085303</v>
       </c>
       <c r="D17">
-        <v>365.0779515800774</v>
+        <v>364.8011831085303</v>
       </c>
       <c r="E17">
-        <v>-9.985000000000007</v>
+        <v>-6.624000000000002</v>
       </c>
       <c r="F17">
-        <v>50.41499999999999</v>
+        <v>53.776</v>
       </c>
       <c r="G17">
         <v>2.91</v>
@@ -2681,28 +2681,28 @@
         <v>24.7</v>
       </c>
       <c r="M17">
-        <v>2.6972025</v>
+        <v>2.877016</v>
       </c>
       <c r="N17">
-        <v>22.0027975</v>
+        <v>21.822984</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>22.0027975</v>
+        <v>21.822984</v>
       </c>
       <c r="Q17">
-        <v>29.0027975</v>
+        <v>28.822984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1638431272284958</v>
+        <v>0.1652484025526445</v>
       </c>
       <c r="T17">
-        <v>1.011131898278517</v>
+        <v>1.023169182781832</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.157636477053542</v>
+        <v>8.585284197237694</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1473686581442214</v>
+        <v>0.1474456581442214</v>
       </c>
       <c r="C18">
-        <v>313.9351831085303</v>
+        <v>310.2978339598092</v>
       </c>
       <c r="D18">
-        <v>364.8011831085303</v>
+        <v>364.5248339598092</v>
       </c>
       <c r="E18">
-        <v>-6.624000000000002</v>
+        <v>-3.262999999999998</v>
       </c>
       <c r="F18">
-        <v>53.776</v>
+        <v>57.137</v>
       </c>
       <c r="G18">
         <v>2.91</v>
@@ -2763,28 +2763,28 @@
         <v>24.7</v>
       </c>
       <c r="M18">
-        <v>2.877016</v>
+        <v>3.0568295</v>
       </c>
       <c r="N18">
-        <v>21.822984</v>
+        <v>21.6431705</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>21.822984</v>
+        <v>21.6431705</v>
       </c>
       <c r="Q18">
-        <v>28.822984</v>
+        <v>28.6431705</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1652484025526445</v>
+        <v>0.1666875399327969</v>
       </c>
       <c r="T18">
-        <v>1.023169182781832</v>
+        <v>1.035496522333421</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.585284197237694</v>
+        <v>8.080267479753124</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1474456581442214</v>
+        <v>0.1475226581442214</v>
       </c>
       <c r="C19">
-        <v>310.2978339598092</v>
+        <v>306.660903181682</v>
       </c>
       <c r="D19">
-        <v>364.5248339598092</v>
+        <v>364.248903181682</v>
       </c>
       <c r="E19">
-        <v>-3.262999999999998</v>
+        <v>0.09799999999999898</v>
       </c>
       <c r="F19">
-        <v>57.137</v>
+        <v>60.498</v>
       </c>
       <c r="G19">
         <v>2.91</v>
@@ -2845,28 +2845,28 @@
         <v>24.7</v>
       </c>
       <c r="M19">
-        <v>3.0568295</v>
+        <v>3.236643</v>
       </c>
       <c r="N19">
-        <v>21.6431705</v>
+        <v>21.463357</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>21.6431705</v>
+        <v>21.463357</v>
       </c>
       <c r="Q19">
-        <v>28.6431705</v>
+        <v>28.463357</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1666875399327969</v>
+        <v>0.1681617782246602</v>
       </c>
       <c r="T19">
-        <v>1.035496522333421</v>
+        <v>1.04812452870334</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.080267479753124</v>
+        <v>7.63136373087795</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1475226581442214</v>
+        <v>0.1477516581442214</v>
       </c>
       <c r="C20">
-        <v>306.6609031816819</v>
+        <v>302.4817409237361</v>
       </c>
       <c r="D20">
-        <v>364.2489031816818</v>
+        <v>363.430740923736</v>
       </c>
       <c r="E20">
-        <v>0.09799999999999187</v>
+        <v>3.458999999999996</v>
       </c>
       <c r="F20">
-        <v>60.49799999999999</v>
+        <v>63.85899999999999</v>
       </c>
       <c r="G20">
         <v>2.91</v>
@@ -2927,45 +2927,45 @@
         <v>24.7</v>
       </c>
       <c r="M20">
-        <v>3.236642999999999</v>
+        <v>3.4675437</v>
       </c>
       <c r="N20">
-        <v>21.463357</v>
+        <v>21.2324563</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>21.463357</v>
+        <v>21.2324563</v>
       </c>
       <c r="Q20">
-        <v>28.463357</v>
+        <v>28.2324563</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1681617782246602</v>
+        <v>0.1696724174620017</v>
       </c>
       <c r="T20">
-        <v>1.04812452870334</v>
+        <v>1.061064337699678</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.631363730877951</v>
+        <v>7.123197899423733</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1477516581442214</v>
+        <v>0.1478366581442214</v>
       </c>
       <c r="C21">
-        <v>302.4817409237361</v>
+        <v>298.8179907794216</v>
       </c>
       <c r="D21">
-        <v>363.430740923736</v>
+        <v>363.1279907794216</v>
       </c>
       <c r="E21">
-        <v>3.458999999999996</v>
+        <v>6.82</v>
       </c>
       <c r="F21">
-        <v>63.85899999999999</v>
+        <v>67.22</v>
       </c>
       <c r="G21">
         <v>2.91</v>
@@ -3009,28 +3009,28 @@
         <v>24.7</v>
       </c>
       <c r="M21">
-        <v>3.4675437</v>
+        <v>3.650046</v>
       </c>
       <c r="N21">
-        <v>21.2324563</v>
+        <v>21.049954</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>21.2324563</v>
+        <v>21.049954</v>
       </c>
       <c r="Q21">
-        <v>28.2324563</v>
+        <v>28.049954</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1696724174620017</v>
+        <v>0.1712208226802767</v>
       </c>
       <c r="T21">
-        <v>1.061064337699678</v>
+        <v>1.074327641920924</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.123197899423733</v>
+        <v>6.767038004452546</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1478366581442214</v>
+        <v>0.1479216581442214</v>
       </c>
       <c r="C22">
-        <v>298.8179907794216</v>
+        <v>295.1547446175676</v>
       </c>
       <c r="D22">
-        <v>363.1279907794216</v>
+        <v>362.8257446175676</v>
       </c>
       <c r="E22">
-        <v>6.82</v>
+        <v>10.181</v>
       </c>
       <c r="F22">
-        <v>67.22</v>
+        <v>70.581</v>
       </c>
       <c r="G22">
         <v>2.91</v>
@@ -3091,28 +3091,28 @@
         <v>24.7</v>
       </c>
       <c r="M22">
-        <v>3.650046</v>
+        <v>3.8325483</v>
       </c>
       <c r="N22">
-        <v>21.049954</v>
+        <v>20.8674517</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>21.049954</v>
+        <v>20.8674517</v>
       </c>
       <c r="Q22">
-        <v>28.049954</v>
+        <v>27.8674517</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1712208226802767</v>
+        <v>0.17280842803066</v>
       </c>
       <c r="T22">
-        <v>1.074327641920924</v>
+        <v>1.087926725995872</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.767038004452546</v>
+        <v>6.444798099478616</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1479216581442214</v>
+        <v>0.1480066581442214</v>
       </c>
       <c r="C23">
-        <v>295.1547446175676</v>
+        <v>291.4920011807656</v>
       </c>
       <c r="D23">
-        <v>362.8257446175676</v>
+        <v>362.5240011807655</v>
       </c>
       <c r="E23">
-        <v>10.18099999999999</v>
+        <v>13.54199999999999</v>
       </c>
       <c r="F23">
-        <v>70.58099999999999</v>
+        <v>73.94199999999999</v>
       </c>
       <c r="G23">
         <v>2.91</v>
@@ -3173,28 +3173,28 @@
         <v>24.7</v>
       </c>
       <c r="M23">
-        <v>3.8325483</v>
+        <v>4.015050599999999</v>
       </c>
       <c r="N23">
-        <v>20.8674517</v>
+        <v>20.6849494</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>20.8674517</v>
+        <v>20.6849494</v>
       </c>
       <c r="Q23">
-        <v>27.8674517</v>
+        <v>27.6849494</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.17280842803066</v>
+        <v>0.1744367412105403</v>
       </c>
       <c r="T23">
-        <v>1.087926725995872</v>
+        <v>1.101874504534281</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.444798099478616</v>
+        <v>6.151852731320497</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1480066581442214</v>
+        <v>0.1483216581442214</v>
       </c>
       <c r="C24">
-        <v>291.4920011807656</v>
+        <v>287.0171383888539</v>
       </c>
       <c r="D24">
-        <v>362.5240011807655</v>
+        <v>361.4101383888539</v>
       </c>
       <c r="E24">
-        <v>13.54199999999999</v>
+        <v>16.903</v>
       </c>
       <c r="F24">
-        <v>73.94199999999999</v>
+        <v>77.303</v>
       </c>
       <c r="G24">
         <v>2.91</v>
@@ -3255,45 +3255,45 @@
         <v>24.7</v>
       </c>
       <c r="M24">
-        <v>4.015050599999999</v>
+        <v>4.2748559</v>
       </c>
       <c r="N24">
-        <v>20.6849494</v>
+        <v>20.4251441</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>20.6849494</v>
+        <v>20.4251441</v>
       </c>
       <c r="Q24">
-        <v>27.6849494</v>
+        <v>27.4251441</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1744367412105403</v>
+        <v>0.1761073482392486</v>
       </c>
       <c r="T24">
-        <v>1.101874504534281</v>
+        <v>1.116184563034726</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.151852731320497</v>
+        <v>5.777972539378461</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1483216581442214</v>
+        <v>0.1484166581442214</v>
       </c>
       <c r="C25">
-        <v>287.0171383888539</v>
+        <v>283.3215536950249</v>
       </c>
       <c r="D25">
-        <v>361.4101383888539</v>
+        <v>361.0755536950248</v>
       </c>
       <c r="E25">
-        <v>16.903</v>
+        <v>20.264</v>
       </c>
       <c r="F25">
-        <v>77.303</v>
+        <v>80.664</v>
       </c>
       <c r="G25">
         <v>2.91</v>
@@ -3337,28 +3337,28 @@
         <v>24.7</v>
       </c>
       <c r="M25">
-        <v>4.2748559</v>
+        <v>4.460719200000001</v>
       </c>
       <c r="N25">
-        <v>20.4251441</v>
+        <v>20.2392808</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>20.4251441</v>
+        <v>20.2392808</v>
       </c>
       <c r="Q25">
-        <v>27.4251441</v>
+        <v>27.2392808</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1761073482392486</v>
+        <v>0.1778219186108176</v>
       </c>
       <c r="T25">
-        <v>1.116184563034726</v>
+        <v>1.130871202022025</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.777972539378461</v>
+        <v>5.537223683571026</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1484166581442214</v>
+        <v>0.1485116581442214</v>
       </c>
       <c r="C26">
-        <v>283.3215536950249</v>
+        <v>279.6265879289105</v>
       </c>
       <c r="D26">
-        <v>361.0755536950248</v>
+        <v>360.7415879289104</v>
       </c>
       <c r="E26">
-        <v>20.26399999999999</v>
+        <v>23.62499999999999</v>
       </c>
       <c r="F26">
-        <v>80.66399999999999</v>
+        <v>84.02499999999999</v>
       </c>
       <c r="G26">
         <v>2.91</v>
@@ -3419,28 +3419,28 @@
         <v>24.7</v>
       </c>
       <c r="M26">
-        <v>4.4607192</v>
+        <v>4.6465825</v>
       </c>
       <c r="N26">
-        <v>20.2392808</v>
+        <v>20.0534175</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>20.2392808</v>
+        <v>20.0534175</v>
       </c>
       <c r="Q26">
-        <v>27.2392808</v>
+        <v>27.0534175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1778219186108176</v>
+        <v>0.1795822108589619</v>
       </c>
       <c r="T26">
-        <v>1.130871202022025</v>
+        <v>1.145949484715652</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.537223683571026</v>
+        <v>5.315734736228184</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1485116581442214</v>
+        <v>0.1486066581442214</v>
       </c>
       <c r="C27">
-        <v>279.6265879289105</v>
+        <v>275.9322393747227</v>
       </c>
       <c r="D27">
-        <v>360.7415879289104</v>
+        <v>360.4082393747227</v>
       </c>
       <c r="E27">
-        <v>23.62499999999999</v>
+        <v>26.986</v>
       </c>
       <c r="F27">
-        <v>84.02499999999999</v>
+        <v>87.386</v>
       </c>
       <c r="G27">
         <v>2.91</v>
@@ -3501,28 +3501,28 @@
         <v>24.7</v>
       </c>
       <c r="M27">
-        <v>4.6465825</v>
+        <v>4.8324458</v>
       </c>
       <c r="N27">
-        <v>20.0534175</v>
+        <v>19.8675542</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>20.0534175</v>
+        <v>19.8675542</v>
       </c>
       <c r="Q27">
-        <v>27.0534175</v>
+        <v>26.8675542</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1795822108589619</v>
+        <v>0.1813900785732722</v>
       </c>
       <c r="T27">
-        <v>1.145949484715652</v>
+        <v>1.161435288563161</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.315734736228184</v>
+        <v>5.111283400219408</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1486066581442214</v>
+        <v>0.1487016581442214</v>
       </c>
       <c r="C28">
-        <v>275.9322393747227</v>
+        <v>272.2385063230103</v>
       </c>
       <c r="D28">
-        <v>360.4082393747227</v>
+        <v>360.0755063230102</v>
       </c>
       <c r="E28">
-        <v>26.986</v>
+        <v>30.347</v>
       </c>
       <c r="F28">
-        <v>87.386</v>
+        <v>90.747</v>
       </c>
       <c r="G28">
         <v>2.91</v>
@@ -3583,28 +3583,28 @@
         <v>24.7</v>
       </c>
       <c r="M28">
-        <v>4.8324458</v>
+        <v>5.0183091</v>
       </c>
       <c r="N28">
-        <v>19.8675542</v>
+        <v>19.6816909</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>19.8675542</v>
+        <v>19.6816909</v>
       </c>
       <c r="Q28">
-        <v>26.8675542</v>
+        <v>26.6816909</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1813900785732722</v>
+        <v>0.1832474769098923</v>
       </c>
       <c r="T28">
-        <v>1.161435288563161</v>
+        <v>1.177345361009232</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.111283400219408</v>
+        <v>4.92197660761869</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1487016581442214</v>
+        <v>0.1487966581442214</v>
       </c>
       <c r="C29">
-        <v>272.2385063230103</v>
+        <v>268.5453870706284</v>
       </c>
       <c r="D29">
-        <v>360.0755063230102</v>
+        <v>359.7433870706284</v>
       </c>
       <c r="E29">
-        <v>30.347</v>
+        <v>33.70800000000001</v>
       </c>
       <c r="F29">
-        <v>90.747</v>
+        <v>94.108</v>
       </c>
       <c r="G29">
         <v>2.91</v>
@@ -3665,28 +3665,28 @@
         <v>24.7</v>
       </c>
       <c r="M29">
-        <v>5.0183091</v>
+        <v>5.2041724</v>
       </c>
       <c r="N29">
-        <v>19.6816909</v>
+        <v>19.4958276</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>19.6816909</v>
+        <v>19.4958276</v>
       </c>
       <c r="Q29">
-        <v>26.6816909</v>
+        <v>26.4958276</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1832474769098923</v>
+        <v>0.1851564696447519</v>
       </c>
       <c r="T29">
-        <v>1.177345361009232</v>
+        <v>1.193697379912138</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.92197660761869</v>
+        <v>4.746191728775164</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1487966581442214</v>
+        <v>0.1488916581442214</v>
       </c>
       <c r="C30">
-        <v>268.5453870706284</v>
+        <v>264.8528799207104</v>
       </c>
       <c r="D30">
-        <v>359.7433870706284</v>
+        <v>359.4118799207104</v>
       </c>
       <c r="E30">
-        <v>33.70800000000001</v>
+        <v>37.06900000000001</v>
       </c>
       <c r="F30">
-        <v>94.108</v>
+        <v>97.46900000000001</v>
       </c>
       <c r="G30">
         <v>2.91</v>
@@ -3747,28 +3747,28 @@
         <v>24.7</v>
       </c>
       <c r="M30">
-        <v>5.2041724</v>
+        <v>5.3900357</v>
       </c>
       <c r="N30">
-        <v>19.4958276</v>
+        <v>19.3099643</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>19.4958276</v>
+        <v>19.3099643</v>
       </c>
       <c r="Q30">
-        <v>26.4958276</v>
+        <v>26.3099643</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1851564696447519</v>
+        <v>0.1871192368228471</v>
       </c>
       <c r="T30">
-        <v>1.193697379912138</v>
+        <v>1.21051001906583</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.746191728775164</v>
+        <v>4.582529945024296</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1488916581442214</v>
+        <v>0.1497366581442214</v>
       </c>
       <c r="C31">
-        <v>264.8528799207104</v>
+        <v>258.5698787331065</v>
       </c>
       <c r="D31">
-        <v>359.4118799207104</v>
+        <v>356.4898787331064</v>
       </c>
       <c r="E31">
-        <v>37.06899999999998</v>
+        <v>40.42999999999999</v>
       </c>
       <c r="F31">
-        <v>97.46899999999998</v>
+        <v>100.83</v>
       </c>
       <c r="G31">
         <v>2.91</v>
@@ -3829,45 +3829,45 @@
         <v>24.7</v>
       </c>
       <c r="M31">
-        <v>5.390035699999999</v>
+        <v>5.827973999999999</v>
       </c>
       <c r="N31">
-        <v>19.3099643</v>
+        <v>18.872026</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>19.3099643</v>
+        <v>18.872026</v>
       </c>
       <c r="Q31">
-        <v>26.3099643</v>
+        <v>25.872026</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.187119236822847</v>
+        <v>0.1891380830631735</v>
       </c>
       <c r="T31">
-        <v>1.21051001906583</v>
+        <v>1.227803019338199</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.582529945024298</v>
+        <v>4.238179511439139</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1497366581442214</v>
+        <v>0.1498566581442214</v>
       </c>
       <c r="C32">
-        <v>258.5698787331065</v>
+        <v>254.7977682264758</v>
       </c>
       <c r="D32">
-        <v>356.4898787331064</v>
+        <v>356.0787682264757</v>
       </c>
       <c r="E32">
-        <v>40.42999999999999</v>
+        <v>43.79099999999999</v>
       </c>
       <c r="F32">
-        <v>100.83</v>
+        <v>104.191</v>
       </c>
       <c r="G32">
         <v>2.91</v>
@@ -3911,28 +3911,28 @@
         <v>24.7</v>
       </c>
       <c r="M32">
-        <v>5.827973999999999</v>
+        <v>6.022239799999999</v>
       </c>
       <c r="N32">
-        <v>18.872026</v>
+        <v>18.6777602</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>18.872026</v>
+        <v>18.6777602</v>
       </c>
       <c r="Q32">
-        <v>25.872026</v>
+        <v>25.6777602</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1891380830631735</v>
+        <v>0.1912154465858281</v>
       </c>
       <c r="T32">
-        <v>1.227803019338199</v>
+        <v>1.245597265995274</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.238179511439139</v>
+        <v>4.101464043328199</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1498566581442214</v>
+        <v>0.1510966581442214</v>
       </c>
       <c r="C33">
-        <v>254.7977682264758</v>
+        <v>247.2434948559566</v>
       </c>
       <c r="D33">
-        <v>356.0787682264757</v>
+        <v>351.8854948559566</v>
       </c>
       <c r="E33">
-        <v>43.79099999999999</v>
+        <v>47.15199999999999</v>
       </c>
       <c r="F33">
-        <v>104.191</v>
+        <v>107.552</v>
       </c>
       <c r="G33">
         <v>2.91</v>
@@ -3993,45 +3993,45 @@
         <v>24.7</v>
       </c>
       <c r="M33">
-        <v>6.022239799999999</v>
+        <v>6.5929376</v>
       </c>
       <c r="N33">
-        <v>18.6777602</v>
+        <v>18.1070624</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>18.6777602</v>
+        <v>18.1070624</v>
       </c>
       <c r="Q33">
-        <v>25.6777602</v>
+        <v>25.1070624</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1912154465858281</v>
+        <v>0.1933539090356197</v>
       </c>
       <c r="T33">
-        <v>1.245597265995274</v>
+        <v>1.263914872848146</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.101464043328199</v>
+        <v>3.746433152954459</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1510966581442214</v>
+        <v>0.1512516581442214</v>
       </c>
       <c r="C34">
-        <v>247.2434948559566</v>
+        <v>243.3652696869783</v>
       </c>
       <c r="D34">
-        <v>351.8854948559566</v>
+        <v>351.3682696869783</v>
       </c>
       <c r="E34">
-        <v>47.15199999999999</v>
+        <v>50.513</v>
       </c>
       <c r="F34">
-        <v>107.552</v>
+        <v>110.913</v>
       </c>
       <c r="G34">
         <v>2.91</v>
@@ -4075,28 +4075,28 @@
         <v>24.7</v>
       </c>
       <c r="M34">
-        <v>6.5929376</v>
+        <v>6.7989669</v>
       </c>
       <c r="N34">
-        <v>18.1070624</v>
+        <v>17.9010331</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>18.1070624</v>
+        <v>17.9010331</v>
       </c>
       <c r="Q34">
-        <v>25.1070624</v>
+        <v>24.9010331</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1933539090356197</v>
+        <v>0.1955562061854051</v>
       </c>
       <c r="T34">
-        <v>1.263914872848146</v>
+        <v>1.282779273935432</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.746433152954459</v>
+        <v>3.632904875592202</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1512516581442214</v>
+        <v>0.1514066581442214</v>
       </c>
       <c r="C35">
-        <v>243.3652696869783</v>
+        <v>239.4885627916129</v>
       </c>
       <c r="D35">
-        <v>351.3682696869783</v>
+        <v>350.8525627916129</v>
       </c>
       <c r="E35">
-        <v>50.513</v>
+        <v>53.874</v>
       </c>
       <c r="F35">
-        <v>110.913</v>
+        <v>114.274</v>
       </c>
       <c r="G35">
         <v>2.91</v>
@@ -4157,28 +4157,28 @@
         <v>24.7</v>
       </c>
       <c r="M35">
-        <v>6.7989669</v>
+        <v>7.0049962</v>
       </c>
       <c r="N35">
-        <v>17.9010331</v>
+        <v>17.6950038</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>17.9010331</v>
+        <v>17.6950038</v>
       </c>
       <c r="Q35">
-        <v>24.9010331</v>
+        <v>24.6950038</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1955562061854051</v>
+        <v>0.1978252396124567</v>
       </c>
       <c r="T35">
-        <v>1.282779273935432</v>
+        <v>1.302215323540514</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.632904875592202</v>
+        <v>3.526054732192431</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1514066581442214</v>
+        <v>0.1525416581442214</v>
       </c>
       <c r="C36">
-        <v>239.4885627916129</v>
+        <v>232.3968950683287</v>
       </c>
       <c r="D36">
-        <v>350.8525627916129</v>
+        <v>347.1218950683286</v>
       </c>
       <c r="E36">
-        <v>53.874</v>
+        <v>57.23500000000001</v>
       </c>
       <c r="F36">
-        <v>114.274</v>
+        <v>117.635</v>
       </c>
       <c r="G36">
         <v>2.91</v>
@@ -4239,45 +4239,45 @@
         <v>24.7</v>
       </c>
       <c r="M36">
-        <v>7.0049962</v>
+        <v>7.540403500000001</v>
       </c>
       <c r="N36">
-        <v>17.6950038</v>
+        <v>17.1595965</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>17.6950038</v>
+        <v>17.1595965</v>
       </c>
       <c r="Q36">
-        <v>24.6950038</v>
+        <v>24.1595965</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1978252396124567</v>
+        <v>0.2001640894526483</v>
       </c>
       <c r="T36">
-        <v>1.302215323540514</v>
+        <v>1.322249405441137</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.526054732192431</v>
+        <v>3.275686771934684</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1525416581442214</v>
+        <v>0.1527246581442214</v>
       </c>
       <c r="C37">
-        <v>232.3968950683287</v>
+        <v>228.4418009847</v>
       </c>
       <c r="D37">
-        <v>347.1218950683286</v>
+        <v>346.5278009846999</v>
       </c>
       <c r="E37">
-        <v>57.23500000000001</v>
+        <v>60.596</v>
       </c>
       <c r="F37">
-        <v>117.635</v>
+        <v>120.996</v>
       </c>
       <c r="G37">
         <v>2.91</v>
@@ -4321,28 +4321,28 @@
         <v>24.7</v>
       </c>
       <c r="M37">
-        <v>7.540403500000001</v>
+        <v>7.7558436</v>
       </c>
       <c r="N37">
-        <v>17.1595965</v>
+        <v>16.9441564</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>17.1595965</v>
+        <v>16.9441564</v>
       </c>
       <c r="Q37">
-        <v>24.1595965</v>
+        <v>23.9441564</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2001640894526483</v>
+        <v>0.2025760283503459</v>
       </c>
       <c r="T37">
-        <v>1.322249405441137</v>
+        <v>1.342909552401155</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.275686771934684</v>
+        <v>3.184695472714277</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1527246581442214</v>
+        <v>0.1529076581442214</v>
       </c>
       <c r="C38">
-        <v>228.4418009846999</v>
+        <v>224.4887369933949</v>
       </c>
       <c r="D38">
-        <v>346.5278009846999</v>
+        <v>345.9357369933949</v>
       </c>
       <c r="E38">
-        <v>60.59599999999998</v>
+        <v>63.95699999999999</v>
       </c>
       <c r="F38">
-        <v>120.996</v>
+        <v>124.357</v>
       </c>
       <c r="G38">
         <v>2.91</v>
@@ -4403,28 +4403,28 @@
         <v>24.7</v>
       </c>
       <c r="M38">
-        <v>7.7558436</v>
+        <v>7.9712837</v>
       </c>
       <c r="N38">
-        <v>16.9441564</v>
+        <v>16.7287163</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>16.9441564</v>
+        <v>16.7287163</v>
       </c>
       <c r="Q38">
-        <v>23.9441564</v>
+        <v>23.7287163</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2025760283503459</v>
+        <v>0.2050645367368594</v>
       </c>
       <c r="T38">
-        <v>1.342909552401155</v>
+        <v>1.364225577042443</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.184695472714277</v>
+        <v>3.098622622100378</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1529076581442214</v>
+        <v>0.1530906581442214</v>
       </c>
       <c r="C39">
-        <v>224.4887369933949</v>
+        <v>220.5376927065504</v>
       </c>
       <c r="D39">
-        <v>345.9357369933949</v>
+        <v>345.3456927065503</v>
       </c>
       <c r="E39">
-        <v>63.95699999999999</v>
+        <v>67.31799999999998</v>
       </c>
       <c r="F39">
-        <v>124.357</v>
+        <v>127.718</v>
       </c>
       <c r="G39">
         <v>2.91</v>
@@ -4485,28 +4485,28 @@
         <v>24.7</v>
       </c>
       <c r="M39">
-        <v>7.9712837</v>
+        <v>8.186723799999999</v>
       </c>
       <c r="N39">
-        <v>16.7287163</v>
+        <v>16.5132762</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>16.7287163</v>
+        <v>16.5132762</v>
       </c>
       <c r="Q39">
-        <v>23.7287163</v>
+        <v>23.5132762</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2050645367368594</v>
+        <v>0.2076333195874539</v>
       </c>
       <c r="T39">
-        <v>1.364225577042443</v>
+        <v>1.386229215381837</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.098622622100378</v>
+        <v>3.017079921518789</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1530906581442214</v>
+        <v>0.1563156581442214</v>
       </c>
       <c r="C40">
-        <v>220.5376927065504</v>
+        <v>207.0990269922023</v>
       </c>
       <c r="D40">
-        <v>345.3456927065503</v>
+        <v>335.2680269922023</v>
       </c>
       <c r="E40">
-        <v>67.31799999999998</v>
+        <v>70.67899999999997</v>
       </c>
       <c r="F40">
-        <v>127.718</v>
+        <v>131.079</v>
       </c>
       <c r="G40">
         <v>2.91</v>
@@ -4567,45 +4567,45 @@
         <v>24.7</v>
       </c>
       <c r="M40">
-        <v>8.186723799999999</v>
+        <v>9.4245801</v>
       </c>
       <c r="N40">
-        <v>16.5132762</v>
+        <v>15.2754199</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>16.5132762</v>
+        <v>15.2754199</v>
       </c>
       <c r="Q40">
-        <v>23.5132762</v>
+        <v>22.2754199</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2076333195874539</v>
+        <v>0.2102863248265925</v>
       </c>
       <c r="T40">
-        <v>1.386229215381837</v>
+        <v>1.408954284486458</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.017079921518789</v>
+        <v>2.620806416616906</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1563156581442214</v>
+        <v>0.1565766581442214</v>
       </c>
       <c r="C41">
-        <v>207.0990269922023</v>
+        <v>202.9481046700192</v>
       </c>
       <c r="D41">
-        <v>335.2680269922023</v>
+        <v>334.4781046700192</v>
       </c>
       <c r="E41">
-        <v>70.67899999999997</v>
+        <v>74.03999999999999</v>
       </c>
       <c r="F41">
-        <v>131.079</v>
+        <v>134.44</v>
       </c>
       <c r="G41">
         <v>2.91</v>
@@ -4649,28 +4649,28 @@
         <v>24.7</v>
       </c>
       <c r="M41">
-        <v>9.4245801</v>
+        <v>9.666236000000001</v>
       </c>
       <c r="N41">
-        <v>15.2754199</v>
+        <v>15.033764</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>15.2754199</v>
+        <v>15.033764</v>
       </c>
       <c r="Q41">
-        <v>22.2754199</v>
+        <v>22.033764</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2102863248265925</v>
+        <v>0.2130277635737023</v>
       </c>
       <c r="T41">
-        <v>1.408954284486458</v>
+        <v>1.432436855894565</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.620806416616906</v>
+        <v>2.555286256201483</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1565766581442214</v>
+        <v>0.1584366581442214</v>
       </c>
       <c r="C42">
-        <v>202.9481046700192</v>
+        <v>194.0637760757916</v>
       </c>
       <c r="D42">
-        <v>334.4781046700192</v>
+        <v>328.9547760757916</v>
       </c>
       <c r="E42">
-        <v>74.03999999999999</v>
+        <v>77.40099999999998</v>
       </c>
       <c r="F42">
-        <v>134.44</v>
+        <v>137.801</v>
       </c>
       <c r="G42">
         <v>2.91</v>
@@ -4731,45 +4731,45 @@
         <v>24.7</v>
       </c>
       <c r="M42">
-        <v>9.666236000000001</v>
+        <v>10.4453158</v>
       </c>
       <c r="N42">
-        <v>15.033764</v>
+        <v>14.2546842</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>15.033764</v>
+        <v>14.2546842</v>
       </c>
       <c r="Q42">
-        <v>22.033764</v>
+        <v>21.2546842</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2130277635737023</v>
+        <v>0.2158621324478329</v>
       </c>
       <c r="T42">
-        <v>1.432436855894565</v>
+        <v>1.456715446672439</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.555286256201483</v>
+        <v>2.364696335940365</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1584366581442214</v>
+        <v>0.1587366581442214</v>
       </c>
       <c r="C43">
-        <v>194.0637760757916</v>
+        <v>189.8289549937412</v>
       </c>
       <c r="D43">
-        <v>328.9547760757916</v>
+        <v>328.0809549937412</v>
       </c>
       <c r="E43">
-        <v>77.40099999999998</v>
+        <v>80.762</v>
       </c>
       <c r="F43">
-        <v>137.801</v>
+        <v>141.162</v>
       </c>
       <c r="G43">
         <v>2.91</v>
@@ -4813,28 +4813,28 @@
         <v>24.7</v>
       </c>
       <c r="M43">
-        <v>10.4453158</v>
+        <v>10.7000796</v>
       </c>
       <c r="N43">
-        <v>14.2546842</v>
+        <v>13.9999204</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>14.2546842</v>
+        <v>13.9999204</v>
       </c>
       <c r="Q43">
-        <v>21.2546842</v>
+        <v>20.9999204</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2158621324478329</v>
+        <v>0.2187942381796921</v>
       </c>
       <c r="T43">
-        <v>1.456715446672439</v>
+        <v>1.481831230235757</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.364696335940365</v>
+        <v>2.308394042227499</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1587366581442214</v>
+        <v>0.1590366581442214</v>
       </c>
       <c r="C44">
-        <v>189.8289549937411</v>
+        <v>185.5987639728195</v>
       </c>
       <c r="D44">
-        <v>328.0809549937411</v>
+        <v>327.2117639728194</v>
       </c>
       <c r="E44">
-        <v>80.76199999999997</v>
+        <v>84.12299999999999</v>
       </c>
       <c r="F44">
-        <v>141.162</v>
+        <v>144.523</v>
       </c>
       <c r="G44">
         <v>2.91</v>
@@ -4895,28 +4895,28 @@
         <v>24.7</v>
       </c>
       <c r="M44">
-        <v>10.7000796</v>
+        <v>10.9548434</v>
       </c>
       <c r="N44">
-        <v>13.9999204</v>
+        <v>13.7451566</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>13.9999204</v>
+        <v>13.7451566</v>
       </c>
       <c r="Q44">
-        <v>20.9999204</v>
+        <v>20.7451566</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2187942381796921</v>
+        <v>0.2218292248144235</v>
       </c>
       <c r="T44">
-        <v>1.481831230235757</v>
+        <v>1.5078282693627</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.308394042227499</v>
+        <v>2.254710459850115</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1590366581442214</v>
+        <v>0.1593366581442214</v>
       </c>
       <c r="C45">
-        <v>185.5987639728195</v>
+        <v>181.3731663107398</v>
       </c>
       <c r="D45">
-        <v>327.2117639728194</v>
+        <v>326.3471663107397</v>
       </c>
       <c r="E45">
-        <v>84.12299999999999</v>
+        <v>87.48399999999998</v>
       </c>
       <c r="F45">
-        <v>144.523</v>
+        <v>147.884</v>
       </c>
       <c r="G45">
         <v>2.91</v>
@@ -4977,28 +4977,28 @@
         <v>24.7</v>
       </c>
       <c r="M45">
-        <v>10.9548434</v>
+        <v>11.2096072</v>
       </c>
       <c r="N45">
-        <v>13.7451566</v>
+        <v>13.4903928</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>13.7451566</v>
+        <v>13.4903928</v>
       </c>
       <c r="Q45">
-        <v>20.7451566</v>
+        <v>20.4903928</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2218292248144235</v>
+        <v>0.2249726038289668</v>
       </c>
       <c r="T45">
-        <v>1.5078282693627</v>
+        <v>1.534753774172748</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.254710459850115</v>
+        <v>2.203467040308067</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1593366581442214</v>
+        <v>0.1596366581442214</v>
       </c>
       <c r="C46">
-        <v>181.3731663107398</v>
+        <v>177.1521256921089</v>
       </c>
       <c r="D46">
-        <v>326.3471663107397</v>
+        <v>325.4871256921089</v>
       </c>
       <c r="E46">
-        <v>87.48399999999998</v>
+        <v>90.84499999999997</v>
       </c>
       <c r="F46">
-        <v>147.884</v>
+        <v>151.245</v>
       </c>
       <c r="G46">
         <v>2.91</v>
@@ -5059,28 +5059,28 @@
         <v>24.7</v>
       </c>
       <c r="M46">
-        <v>11.2096072</v>
+        <v>11.464371</v>
       </c>
       <c r="N46">
-        <v>13.4903928</v>
+        <v>13.235629</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>13.4903928</v>
+        <v>13.235629</v>
       </c>
       <c r="Q46">
-        <v>20.4903928</v>
+        <v>20.235629</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2249726038289668</v>
+        <v>0.228230287534948</v>
       </c>
       <c r="T46">
-        <v>1.534753774172748</v>
+        <v>1.562658388248616</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.203467040308067</v>
+        <v>2.154501106078999</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1596366581442214</v>
+        <v>0.1599366581442214</v>
       </c>
       <c r="C47">
-        <v>177.1521256921089</v>
+        <v>172.9356061833439</v>
       </c>
       <c r="D47">
-        <v>325.4871256921089</v>
+        <v>324.6316061833438</v>
       </c>
       <c r="E47">
-        <v>90.84499999999997</v>
+        <v>94.20599999999999</v>
       </c>
       <c r="F47">
-        <v>151.245</v>
+        <v>154.606</v>
       </c>
       <c r="G47">
         <v>2.91</v>
@@ -5141,28 +5141,28 @@
         <v>24.7</v>
       </c>
       <c r="M47">
-        <v>11.464371</v>
+        <v>11.7191348</v>
       </c>
       <c r="N47">
-        <v>13.235629</v>
+        <v>12.9808652</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>13.235629</v>
+        <v>12.9808652</v>
       </c>
       <c r="Q47">
-        <v>20.235629</v>
+        <v>19.9808652</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.228230287534948</v>
+        <v>0.2316086261930026</v>
       </c>
       <c r="T47">
-        <v>1.562658388248616</v>
+        <v>1.591596506549517</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.154501106078999</v>
+        <v>2.107664125512064</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1599366581442214</v>
+        <v>0.1602366581442214</v>
       </c>
       <c r="C48">
-        <v>172.9356061833439</v>
+        <v>168.7235722276662</v>
       </c>
       <c r="D48">
-        <v>324.6316061833438</v>
+        <v>323.7805722276662</v>
       </c>
       <c r="E48">
-        <v>94.20599999999999</v>
+        <v>97.56699999999998</v>
       </c>
       <c r="F48">
-        <v>154.606</v>
+        <v>157.967</v>
       </c>
       <c r="G48">
         <v>2.91</v>
@@ -5223,28 +5223,28 @@
         <v>24.7</v>
       </c>
       <c r="M48">
-        <v>11.7191348</v>
+        <v>11.9738986</v>
       </c>
       <c r="N48">
-        <v>12.9808652</v>
+        <v>12.7261014</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>12.9808652</v>
+        <v>12.7261014</v>
       </c>
       <c r="Q48">
-        <v>19.9808652</v>
+        <v>19.7261014</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2316086261930026</v>
+        <v>0.2351144493287196</v>
       </c>
       <c r="T48">
-        <v>1.591596506549517</v>
+        <v>1.621626629314602</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.107664125512064</v>
+        <v>2.062820207947977</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1602366581442214</v>
+        <v>0.1605366581442214</v>
       </c>
       <c r="C49">
-        <v>168.7235722276662</v>
+        <v>164.5159886401766</v>
       </c>
       <c r="D49">
-        <v>323.7805722276662</v>
+        <v>322.9339886401766</v>
       </c>
       <c r="E49">
-        <v>97.56699999999998</v>
+        <v>100.928</v>
       </c>
       <c r="F49">
-        <v>157.967</v>
+        <v>161.328</v>
       </c>
       <c r="G49">
         <v>2.91</v>
@@ -5305,28 +5305,28 @@
         <v>24.7</v>
       </c>
       <c r="M49">
-        <v>11.9738986</v>
+        <v>12.2286624</v>
       </c>
       <c r="N49">
-        <v>12.7261014</v>
+        <v>12.4713376</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>12.7261014</v>
+        <v>12.4713376</v>
       </c>
       <c r="Q49">
-        <v>19.7261014</v>
+        <v>19.4713376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2351144493287196</v>
+        <v>0.2387551118158104</v>
       </c>
       <c r="T49">
-        <v>1.621626629314602</v>
+        <v>1.652811756801421</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.062820207947977</v>
+        <v>2.019844786949061</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1605366581442214</v>
+        <v>0.1677946581442214</v>
       </c>
       <c r="C50">
-        <v>164.5159886401768</v>
+        <v>141.9422220715003</v>
       </c>
       <c r="D50">
-        <v>322.9339886401767</v>
+        <v>303.7212220715003</v>
       </c>
       <c r="E50">
-        <v>100.928</v>
+        <v>104.289</v>
       </c>
       <c r="F50">
-        <v>161.328</v>
+        <v>164.689</v>
       </c>
       <c r="G50">
         <v>2.91</v>
@@ -5387,45 +5387,45 @@
         <v>24.7</v>
       </c>
       <c r="M50">
-        <v>12.2286624</v>
+        <v>14.82201</v>
       </c>
       <c r="N50">
-        <v>12.4713376</v>
+        <v>9.87799</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>12.4713376</v>
+        <v>9.87799</v>
       </c>
       <c r="Q50">
-        <v>19.4713376</v>
+        <v>16.87799</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2387551118158104</v>
+        <v>0.2425385453808263</v>
       </c>
       <c r="T50">
-        <v>1.652811756801421</v>
+        <v>1.685219830464194</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.019844786949061</v>
+        <v>1.666440651436614</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1677946581442214</v>
+        <v>0.1682366581442214</v>
       </c>
       <c r="C51">
-        <v>141.9422220715003</v>
+        <v>137.4847793705123</v>
       </c>
       <c r="D51">
-        <v>303.7212220715003</v>
+        <v>302.6247793705122</v>
       </c>
       <c r="E51">
-        <v>104.289</v>
+        <v>107.65</v>
       </c>
       <c r="F51">
-        <v>164.689</v>
+        <v>168.05</v>
       </c>
       <c r="G51">
         <v>2.91</v>
@@ -5469,28 +5469,28 @@
         <v>24.7</v>
       </c>
       <c r="M51">
-        <v>14.82201</v>
+        <v>15.1245</v>
       </c>
       <c r="N51">
-        <v>9.87799</v>
+        <v>9.575500000000002</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>9.87799</v>
+        <v>9.575500000000002</v>
       </c>
       <c r="Q51">
-        <v>16.87799</v>
+        <v>16.5755</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2425385453808263</v>
+        <v>0.2464733162884428</v>
       </c>
       <c r="T51">
-        <v>1.685219830464194</v>
+        <v>1.718924227073478</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.666440651436614</v>
+        <v>1.633111838407881</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1682366581442214</v>
+        <v>0.1686786581442214</v>
       </c>
       <c r="C52">
-        <v>137.4847793705123</v>
+        <v>133.0352245758727</v>
       </c>
       <c r="D52">
-        <v>302.6247793705122</v>
+        <v>301.5362245758727</v>
       </c>
       <c r="E52">
-        <v>107.65</v>
+        <v>111.011</v>
       </c>
       <c r="F52">
-        <v>168.05</v>
+        <v>171.411</v>
       </c>
       <c r="G52">
         <v>2.91</v>
@@ -5551,28 +5551,28 @@
         <v>24.7</v>
       </c>
       <c r="M52">
-        <v>15.1245</v>
+        <v>15.42699</v>
       </c>
       <c r="N52">
-        <v>9.575500000000002</v>
+        <v>9.273010000000003</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>9.575500000000002</v>
+        <v>9.273010000000003</v>
       </c>
       <c r="Q52">
-        <v>16.5755</v>
+        <v>16.27301</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2464733162884428</v>
+        <v>0.2505686900902477</v>
       </c>
       <c r="T52">
-        <v>1.718924227073478</v>
+        <v>1.754004313340284</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.633111838407881</v>
+        <v>1.601090037654786</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1686786581442214</v>
+        <v>0.1691206581442214</v>
       </c>
       <c r="C53">
-        <v>133.0352245758727</v>
+        <v>128.5934728732126</v>
       </c>
       <c r="D53">
-        <v>301.5362245758727</v>
+        <v>300.4554728732126</v>
       </c>
       <c r="E53">
-        <v>111.011</v>
+        <v>114.372</v>
       </c>
       <c r="F53">
-        <v>171.411</v>
+        <v>174.772</v>
       </c>
       <c r="G53">
         <v>2.91</v>
@@ -5633,28 +5633,28 @@
         <v>24.7</v>
       </c>
       <c r="M53">
-        <v>15.42699</v>
+        <v>15.72948</v>
       </c>
       <c r="N53">
-        <v>9.273010000000003</v>
+        <v>8.97052</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>9.273010000000003</v>
+        <v>8.97052</v>
       </c>
       <c r="Q53">
-        <v>16.27301</v>
+        <v>15.97052</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2505686900902477</v>
+        <v>0.2548347044671279</v>
       </c>
       <c r="T53">
-        <v>1.754004313340284</v>
+        <v>1.790546069868207</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.601090037654786</v>
+        <v>1.570299844622963</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1691206581442214</v>
+        <v>0.1695626581442214</v>
       </c>
       <c r="C54">
-        <v>128.5934728732126</v>
+        <v>124.1594406597706</v>
       </c>
       <c r="D54">
-        <v>300.4554728732126</v>
+        <v>299.3824406597705</v>
       </c>
       <c r="E54">
-        <v>114.372</v>
+        <v>117.733</v>
       </c>
       <c r="F54">
-        <v>174.772</v>
+        <v>178.133</v>
       </c>
       <c r="G54">
         <v>2.91</v>
@@ -5715,28 +5715,28 @@
         <v>24.7</v>
       </c>
       <c r="M54">
-        <v>15.72948</v>
+        <v>16.03197</v>
       </c>
       <c r="N54">
-        <v>8.97052</v>
+        <v>8.668030000000002</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>8.97052</v>
+        <v>8.668030000000002</v>
       </c>
       <c r="Q54">
-        <v>15.97052</v>
+        <v>15.66803</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2548347044671279</v>
+        <v>0.2592822513706838</v>
       </c>
       <c r="T54">
-        <v>1.790546069868207</v>
+        <v>1.828642794759019</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.570299844622963</v>
+        <v>1.540671545667813</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1695626581442214</v>
+        <v>0.1700046581442214</v>
       </c>
       <c r="C55">
-        <v>124.1594406597706</v>
+        <v>119.7330455228348</v>
       </c>
       <c r="D55">
-        <v>299.3824406597705</v>
+        <v>298.3170455228348</v>
       </c>
       <c r="E55">
-        <v>117.733</v>
+        <v>121.094</v>
       </c>
       <c r="F55">
-        <v>178.133</v>
+        <v>181.494</v>
       </c>
       <c r="G55">
         <v>2.91</v>
@@ -5797,28 +5797,28 @@
         <v>24.7</v>
       </c>
       <c r="M55">
-        <v>16.03197</v>
+        <v>16.33446</v>
       </c>
       <c r="N55">
-        <v>8.668030000000002</v>
+        <v>8.365539999999999</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>8.668030000000002</v>
+        <v>8.365539999999999</v>
       </c>
       <c r="Q55">
-        <v>15.66803</v>
+        <v>15.36554</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2592822513706838</v>
+        <v>0.2639231698787421</v>
       </c>
       <c r="T55">
-        <v>1.828642794759019</v>
+        <v>1.868395898992911</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.540671545667813</v>
+        <v>1.512140591118408</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1700046581442214</v>
+        <v>0.2016866581442214</v>
       </c>
       <c r="C56">
-        <v>119.7330455228348</v>
+        <v>55.74286308497392</v>
       </c>
       <c r="D56">
-        <v>298.3170455228348</v>
+        <v>237.6878630849739</v>
       </c>
       <c r="E56">
-        <v>121.094</v>
+        <v>124.455</v>
       </c>
       <c r="F56">
-        <v>181.494</v>
+        <v>184.855</v>
       </c>
       <c r="G56">
         <v>2.91</v>
@@ -5879,45 +5879,45 @@
         <v>24.7</v>
       </c>
       <c r="M56">
-        <v>16.33446</v>
+        <v>27.136714</v>
       </c>
       <c r="N56">
-        <v>8.365539999999999</v>
+        <v>-2.436714000000002</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P56">
-        <v>8.365539999999999</v>
+        <v>-2.436714000000002</v>
       </c>
       <c r="Q56">
-        <v>15.36554</v>
+        <v>4.563285999999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2639231698787421</v>
+        <v>0.2687703514316031</v>
       </c>
       <c r="T56">
-        <v>1.868395898992911</v>
+        <v>1.90991580785942</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.512140591118408</v>
+        <v>0.9102060035713977</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2016866581442214</v>
+        <v>0.2026966581442214</v>
       </c>
       <c r="C57">
-        <v>55.74286308497392</v>
+        <v>50.85178115362294</v>
       </c>
       <c r="D57">
-        <v>237.6878630849739</v>
+        <v>236.1577811536229</v>
       </c>
       <c r="E57">
-        <v>124.455</v>
+        <v>127.816</v>
       </c>
       <c r="F57">
-        <v>184.855</v>
+        <v>188.216</v>
       </c>
       <c r="G57">
         <v>2.91</v>
@@ -5961,28 +5961,28 @@
         <v>24.7</v>
       </c>
       <c r="M57">
-        <v>27.136714</v>
+        <v>27.6301088</v>
       </c>
       <c r="N57">
-        <v>-2.436714000000002</v>
+        <v>-2.930108800000003</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-2.436714000000002</v>
+        <v>-2.930108800000003</v>
       </c>
       <c r="Q57">
-        <v>4.563285999999998</v>
+        <v>4.069891199999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2687703514316031</v>
+        <v>0.273837859418685</v>
       </c>
       <c r="T57">
-        <v>1.90991580785942</v>
+        <v>1.953322985310771</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9102060035713977</v>
+        <v>0.8939523249361941</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2026966581442214</v>
+        <v>0.2037066581442214</v>
       </c>
       <c r="C58">
-        <v>50.85178115362294</v>
+        <v>45.98027259262665</v>
       </c>
       <c r="D58">
-        <v>236.1577811536229</v>
+        <v>234.6472725926266</v>
       </c>
       <c r="E58">
-        <v>127.816</v>
+        <v>131.177</v>
       </c>
       <c r="F58">
-        <v>188.216</v>
+        <v>191.577</v>
       </c>
       <c r="G58">
         <v>2.91</v>
@@ -6043,28 +6043,28 @@
         <v>24.7</v>
       </c>
       <c r="M58">
-        <v>27.6301088</v>
+        <v>28.1235036</v>
       </c>
       <c r="N58">
-        <v>-2.930108800000003</v>
+        <v>-3.423503600000004</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-2.930108800000003</v>
+        <v>-3.423503600000004</v>
       </c>
       <c r="Q58">
-        <v>4.069891199999997</v>
+        <v>3.576496399999996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.273837859418685</v>
+        <v>0.2791410654516777</v>
       </c>
       <c r="T58">
-        <v>1.953322985310771</v>
+        <v>1.998749101248231</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8939523249361941</v>
+        <v>0.8782689508145065</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2037066581442214</v>
+        <v>0.2047166581442214</v>
       </c>
       <c r="C59">
-        <v>45.98027259262665</v>
+        <v>41.12796420440546</v>
       </c>
       <c r="D59">
-        <v>234.6472725926266</v>
+        <v>233.1559642044055</v>
       </c>
       <c r="E59">
-        <v>131.177</v>
+        <v>134.538</v>
       </c>
       <c r="F59">
-        <v>191.577</v>
+        <v>194.938</v>
       </c>
       <c r="G59">
         <v>2.91</v>
@@ -6125,28 +6125,28 @@
         <v>24.7</v>
       </c>
       <c r="M59">
-        <v>28.1235036</v>
+        <v>28.6168984</v>
       </c>
       <c r="N59">
-        <v>-3.423503600000004</v>
+        <v>-3.916898400000004</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-3.423503600000004</v>
+        <v>-3.916898400000004</v>
       </c>
       <c r="Q59">
-        <v>3.576496399999996</v>
+        <v>3.083101599999996</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2791410654516777</v>
+        <v>0.2846968051052891</v>
       </c>
       <c r="T59">
-        <v>1.998749101248231</v>
+        <v>2.046338365563665</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8782689508145065</v>
+        <v>0.863126382697015</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2047166581442214</v>
+        <v>0.2057266581442214</v>
       </c>
       <c r="C60">
-        <v>41.12796420440554</v>
+        <v>36.29449221894023</v>
       </c>
       <c r="D60">
-        <v>233.1559642044055</v>
+        <v>231.6834922189402</v>
       </c>
       <c r="E60">
-        <v>134.538</v>
+        <v>137.899</v>
       </c>
       <c r="F60">
-        <v>194.938</v>
+        <v>198.299</v>
       </c>
       <c r="G60">
         <v>2.91</v>
@@ -6207,28 +6207,28 @@
         <v>24.7</v>
       </c>
       <c r="M60">
-        <v>28.6168984</v>
+        <v>29.1102932</v>
       </c>
       <c r="N60">
-        <v>-3.916898399999997</v>
+        <v>-4.410293200000002</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-3.916898399999997</v>
+        <v>-4.410293200000002</v>
       </c>
       <c r="Q60">
-        <v>3.083101600000003</v>
+        <v>2.589706799999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.284696805105289</v>
+        <v>0.2905235564493204</v>
       </c>
       <c r="T60">
-        <v>2.046338365563664</v>
+        <v>2.09624905740668</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8631263826970152</v>
+        <v>0.8484971219733368</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2057266581442214</v>
+        <v>0.2067366581442214</v>
       </c>
       <c r="C61">
-        <v>36.29449221894023</v>
+        <v>31.47950199794639</v>
       </c>
       <c r="D61">
-        <v>231.6834922189402</v>
+        <v>230.2295019979464</v>
       </c>
       <c r="E61">
-        <v>137.899</v>
+        <v>141.26</v>
       </c>
       <c r="F61">
-        <v>198.299</v>
+        <v>201.66</v>
       </c>
       <c r="G61">
         <v>2.91</v>
@@ -6289,28 +6289,28 @@
         <v>24.7</v>
       </c>
       <c r="M61">
-        <v>29.1102932</v>
+        <v>29.603688</v>
       </c>
       <c r="N61">
-        <v>-4.410293200000002</v>
+        <v>-4.903687999999999</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-4.410293200000002</v>
+        <v>-4.903687999999999</v>
       </c>
       <c r="Q61">
-        <v>2.589706799999998</v>
+        <v>2.096312000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2905235564493204</v>
+        <v>0.2966416453605535</v>
       </c>
       <c r="T61">
-        <v>2.09624905740668</v>
+        <v>2.148655283841848</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8484971219733368</v>
+        <v>0.8343555032737813</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2067366581442214</v>
+        <v>0.2077466581442214</v>
       </c>
       <c r="C62">
-        <v>31.47950199794639</v>
+        <v>26.68264775011838</v>
       </c>
       <c r="D62">
-        <v>230.2295019979464</v>
+        <v>228.7936477501184</v>
       </c>
       <c r="E62">
-        <v>141.26</v>
+        <v>144.621</v>
       </c>
       <c r="F62">
-        <v>201.66</v>
+        <v>205.021</v>
       </c>
       <c r="G62">
         <v>2.91</v>
@@ -6371,28 +6371,28 @@
         <v>24.7</v>
       </c>
       <c r="M62">
-        <v>29.603688</v>
+        <v>30.0970828</v>
       </c>
       <c r="N62">
-        <v>-4.903687999999999</v>
+        <v>-5.397082800000003</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-4.903687999999999</v>
+        <v>-5.397082800000003</v>
       </c>
       <c r="Q62">
-        <v>2.096312000000001</v>
+        <v>1.602917199999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2966416453605535</v>
+        <v>0.3030734824210805</v>
       </c>
       <c r="T62">
-        <v>2.148655283841848</v>
+        <v>2.203749009068562</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8343555032737813</v>
+        <v>0.8206775442037192</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2077466581442214</v>
+        <v>0.2087566581442214</v>
       </c>
       <c r="C63">
-        <v>26.68264775011838</v>
+        <v>21.90359225696318</v>
       </c>
       <c r="D63">
-        <v>228.7936477501184</v>
+        <v>227.3755922569632</v>
       </c>
       <c r="E63">
-        <v>144.621</v>
+        <v>147.982</v>
       </c>
       <c r="F63">
-        <v>205.021</v>
+        <v>208.382</v>
       </c>
       <c r="G63">
         <v>2.91</v>
@@ -6453,28 +6453,28 @@
         <v>24.7</v>
       </c>
       <c r="M63">
-        <v>30.0970828</v>
+        <v>30.5904776</v>
       </c>
       <c r="N63">
-        <v>-5.397082800000003</v>
+        <v>-5.890477600000001</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-5.397082800000003</v>
+        <v>-5.890477600000001</v>
       </c>
       <c r="Q63">
-        <v>1.602917199999997</v>
+        <v>1.109522399999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3030734824210805</v>
+        <v>0.3098438372216353</v>
       </c>
       <c r="T63">
-        <v>2.203749009068562</v>
+        <v>2.26174240404405</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8206775442037192</v>
+        <v>0.8074408096197884</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2087566581442214</v>
+        <v>0.2437866581442214</v>
       </c>
       <c r="C64">
-        <v>21.90359225696318</v>
+        <v>-21.68722459746044</v>
       </c>
       <c r="D64">
-        <v>227.3755922569632</v>
+        <v>187.1457754025395</v>
       </c>
       <c r="E64">
-        <v>147.982</v>
+        <v>151.343</v>
       </c>
       <c r="F64">
-        <v>208.382</v>
+        <v>211.743</v>
       </c>
       <c r="G64">
         <v>2.91</v>
@@ -6535,45 +6535,45 @@
         <v>24.7</v>
       </c>
       <c r="M64">
-        <v>30.5904776</v>
+        <v>42.51799439999999</v>
       </c>
       <c r="N64">
-        <v>-5.890477600000001</v>
+        <v>-17.81799439999999</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-5.890477600000001</v>
+        <v>-17.81799439999999</v>
       </c>
       <c r="Q64">
-        <v>1.109522399999999</v>
+        <v>-10.81799439999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3098438372216353</v>
+        <v>0.3169801571465443</v>
       </c>
       <c r="T64">
-        <v>2.26174240404405</v>
+        <v>2.322870577126322</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8074408096197884</v>
+        <v>0.5809305059788992</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2437866581442214</v>
+        <v>0.2453366581442214</v>
       </c>
       <c r="C65">
-        <v>-21.68722459746044</v>
+        <v>-26.50197226754665</v>
       </c>
       <c r="D65">
-        <v>187.1457754025395</v>
+        <v>185.6920277324533</v>
       </c>
       <c r="E65">
-        <v>151.343</v>
+        <v>154.704</v>
       </c>
       <c r="F65">
-        <v>211.743</v>
+        <v>215.104</v>
       </c>
       <c r="G65">
         <v>2.91</v>
@@ -6617,28 +6617,28 @@
         <v>24.7</v>
       </c>
       <c r="M65">
-        <v>42.51799439999999</v>
+        <v>43.1928832</v>
       </c>
       <c r="N65">
-        <v>-17.81799439999999</v>
+        <v>-18.4928832</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-17.81799439999999</v>
+        <v>-18.4928832</v>
       </c>
       <c r="Q65">
-        <v>-10.81799439999999</v>
+        <v>-11.4928832</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3169801571465443</v>
+        <v>0.3245129392895039</v>
       </c>
       <c r="T65">
-        <v>2.322870577126322</v>
+        <v>2.387394759824275</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5809305059788992</v>
+        <v>0.5718534668229789</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2453366581442214</v>
+        <v>0.2468866581442214</v>
       </c>
       <c r="C66">
-        <v>-26.50197226754665</v>
+        <v>-31.29430861597245</v>
       </c>
       <c r="D66">
-        <v>185.6920277324533</v>
+        <v>184.2606913840275</v>
       </c>
       <c r="E66">
-        <v>154.704</v>
+        <v>158.065</v>
       </c>
       <c r="F66">
-        <v>215.104</v>
+        <v>218.465</v>
       </c>
       <c r="G66">
         <v>2.91</v>
@@ -6699,28 +6699,28 @@
         <v>24.7</v>
       </c>
       <c r="M66">
-        <v>43.1928832</v>
+        <v>43.867772</v>
       </c>
       <c r="N66">
-        <v>-18.4928832</v>
+        <v>-19.167772</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-18.4928832</v>
+        <v>-19.167772</v>
       </c>
       <c r="Q66">
-        <v>-11.4928832</v>
+        <v>-12.167772</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3245129392895039</v>
+        <v>0.3324761661263469</v>
       </c>
       <c r="T66">
-        <v>2.387394759824275</v>
+        <v>2.455606038676398</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5718534668229789</v>
+        <v>0.5630557211795484</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2468866581442214</v>
+        <v>0.2484366581442214</v>
       </c>
       <c r="C67">
-        <v>-31.29430861597245</v>
+        <v>-36.06474792602054</v>
       </c>
       <c r="D67">
-        <v>184.2606913840275</v>
+        <v>182.8512520739795</v>
       </c>
       <c r="E67">
-        <v>158.065</v>
+        <v>161.426</v>
       </c>
       <c r="F67">
-        <v>218.465</v>
+        <v>221.826</v>
       </c>
       <c r="G67">
         <v>2.91</v>
@@ -6781,28 +6781,28 @@
         <v>24.7</v>
       </c>
       <c r="M67">
-        <v>43.867772</v>
+        <v>44.5426608</v>
       </c>
       <c r="N67">
-        <v>-19.167772</v>
+        <v>-19.8426608</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-19.167772</v>
+        <v>-19.8426608</v>
       </c>
       <c r="Q67">
-        <v>-12.167772</v>
+        <v>-12.8426608</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3324761661263469</v>
+        <v>0.3409078180712394</v>
       </c>
       <c r="T67">
-        <v>2.455606038676398</v>
+        <v>2.527829745696291</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5630557211795484</v>
+        <v>0.5545245738889492</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2484366581442214</v>
+        <v>0.2499866581442214</v>
       </c>
       <c r="C68">
-        <v>-36.06474792602054</v>
+        <v>-40.81378886508369</v>
       </c>
       <c r="D68">
-        <v>182.8512520739795</v>
+        <v>181.4632111349163</v>
       </c>
       <c r="E68">
-        <v>161.426</v>
+        <v>164.787</v>
       </c>
       <c r="F68">
-        <v>221.826</v>
+        <v>225.187</v>
       </c>
       <c r="G68">
         <v>2.91</v>
@@ -6863,28 +6863,28 @@
         <v>24.7</v>
       </c>
       <c r="M68">
-        <v>44.5426608</v>
+        <v>45.2175496</v>
       </c>
       <c r="N68">
-        <v>-19.8426608</v>
+        <v>-20.5175496</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-19.8426608</v>
+        <v>-20.5175496</v>
       </c>
       <c r="Q68">
-        <v>-12.8426608</v>
+        <v>-13.5175496</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3409078180712394</v>
+        <v>0.3498504792249134</v>
       </c>
       <c r="T68">
-        <v>2.527829745696291</v>
+        <v>2.604430647081028</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5545245738889492</v>
+        <v>0.5462480877115021</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2499866581442214</v>
+        <v>0.2515366581442214</v>
       </c>
       <c r="C69">
-        <v>-40.81378886508369</v>
+        <v>-45.54191507290787</v>
       </c>
       <c r="D69">
-        <v>181.4632111349163</v>
+        <v>180.0960849270921</v>
       </c>
       <c r="E69">
-        <v>164.787</v>
+        <v>168.148</v>
       </c>
       <c r="F69">
-        <v>225.187</v>
+        <v>228.548</v>
       </c>
       <c r="G69">
         <v>2.91</v>
@@ -6945,28 +6945,28 @@
         <v>24.7</v>
       </c>
       <c r="M69">
-        <v>45.2175496</v>
+        <v>45.8924384</v>
       </c>
       <c r="N69">
-        <v>-20.5175496</v>
+        <v>-21.1924384</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-20.5175496</v>
+        <v>-21.1924384</v>
       </c>
       <c r="Q69">
-        <v>-13.5175496</v>
+        <v>-14.1924384</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3498504792249134</v>
+        <v>0.3593520567006919</v>
       </c>
       <c r="T69">
-        <v>2.604430647081028</v>
+        <v>2.68581910480231</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5462480877115021</v>
+        <v>0.5382150275980977</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2515366581442214</v>
+        <v>0.2530866581442214</v>
       </c>
       <c r="C70">
-        <v>-45.54191507290787</v>
+        <v>-50.24959572344329</v>
       </c>
       <c r="D70">
-        <v>180.0960849270921</v>
+        <v>178.7494042765567</v>
       </c>
       <c r="E70">
-        <v>168.148</v>
+        <v>171.509</v>
       </c>
       <c r="F70">
-        <v>228.548</v>
+        <v>231.909</v>
       </c>
       <c r="G70">
         <v>2.91</v>
@@ -7027,28 +7027,28 @@
         <v>24.7</v>
       </c>
       <c r="M70">
-        <v>45.8924384</v>
+        <v>46.5673272</v>
       </c>
       <c r="N70">
-        <v>-21.1924384</v>
+        <v>-21.8673272</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-21.1924384</v>
+        <v>-21.8673272</v>
       </c>
       <c r="Q70">
-        <v>-14.1924384</v>
+        <v>-14.8673272</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3593520567006919</v>
+        <v>0.3694666391749078</v>
       </c>
       <c r="T70">
-        <v>2.68581910480231</v>
+        <v>2.772458430763675</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5382150275980977</v>
+        <v>0.5304148098068209</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2530866581442214</v>
+        <v>0.2546366581442214</v>
       </c>
       <c r="C71">
-        <v>-50.24959572344329</v>
+        <v>-54.93728606167571</v>
       </c>
       <c r="D71">
-        <v>178.7494042765567</v>
+        <v>177.4227139383243</v>
       </c>
       <c r="E71">
-        <v>171.509</v>
+        <v>174.87</v>
       </c>
       <c r="F71">
-        <v>231.909</v>
+        <v>235.27</v>
       </c>
       <c r="G71">
         <v>2.91</v>
@@ -7109,28 +7109,28 @@
         <v>24.7</v>
       </c>
       <c r="M71">
-        <v>46.5673272</v>
+        <v>47.24221600000001</v>
       </c>
       <c r="N71">
-        <v>-21.8673272</v>
+        <v>-22.54221600000001</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-21.8673272</v>
+        <v>-22.54221600000001</v>
       </c>
       <c r="Q71">
-        <v>-14.8673272</v>
+        <v>-15.54221600000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3694666391749078</v>
+        <v>0.3802555271474047</v>
       </c>
       <c r="T71">
-        <v>2.772458430763675</v>
+        <v>2.864873711789131</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5304148098068209</v>
+        <v>0.5228374553810091</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2546366581442214</v>
+        <v>0.2561866581442214</v>
       </c>
       <c r="C72">
-        <v>-54.93728606167571</v>
+        <v>-59.60542791672569</v>
       </c>
       <c r="D72">
-        <v>177.4227139383243</v>
+        <v>176.1155720832743</v>
       </c>
       <c r="E72">
-        <v>174.87</v>
+        <v>178.231</v>
       </c>
       <c r="F72">
-        <v>235.27</v>
+        <v>238.631</v>
       </c>
       <c r="G72">
         <v>2.91</v>
@@ -7191,28 +7191,28 @@
         <v>24.7</v>
       </c>
       <c r="M72">
-        <v>47.24221600000001</v>
+        <v>47.9171048</v>
       </c>
       <c r="N72">
-        <v>-22.54221600000001</v>
+        <v>-23.2171048</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-22.54221600000001</v>
+        <v>-23.2171048</v>
       </c>
       <c r="Q72">
-        <v>-15.54221600000001</v>
+        <v>-16.2171048</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3802555271474047</v>
+        <v>0.3917884763593842</v>
       </c>
       <c r="T72">
-        <v>2.864873711789131</v>
+        <v>2.963662460471515</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5228374553810091</v>
+        <v>0.5154735475587414</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2561866581442214</v>
+        <v>0.2577366581442214</v>
       </c>
       <c r="C73">
-        <v>-59.60542791672566</v>
+        <v>-64.2544501924346</v>
       </c>
       <c r="D73">
-        <v>176.1155720832743</v>
+        <v>174.8275498075654</v>
       </c>
       <c r="E73">
-        <v>178.231</v>
+        <v>181.592</v>
       </c>
       <c r="F73">
-        <v>238.631</v>
+        <v>241.992</v>
       </c>
       <c r="G73">
         <v>2.91</v>
@@ -7273,28 +7273,28 @@
         <v>24.7</v>
       </c>
       <c r="M73">
-        <v>47.9171048</v>
+        <v>48.5919936</v>
       </c>
       <c r="N73">
-        <v>-23.2171048</v>
+        <v>-23.8919936</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-23.2171048</v>
+        <v>-23.8919936</v>
       </c>
       <c r="Q73">
-        <v>-16.2171048</v>
+        <v>-16.8919936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3917884763593841</v>
+        <v>0.4041452076579335</v>
       </c>
       <c r="T73">
-        <v>2.963662460471514</v>
+        <v>3.069507548345496</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5154735475587415</v>
+        <v>0.5083141927315368</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2577366581442214</v>
+        <v>0.2592866581442214</v>
       </c>
       <c r="C74">
-        <v>-64.2544501924346</v>
+        <v>-68.88476933657827</v>
       </c>
       <c r="D74">
-        <v>174.8275498075654</v>
+        <v>173.5582306634217</v>
       </c>
       <c r="E74">
-        <v>181.592</v>
+        <v>184.953</v>
       </c>
       <c r="F74">
-        <v>241.992</v>
+        <v>245.353</v>
       </c>
       <c r="G74">
         <v>2.91</v>
@@ -7355,28 +7355,28 @@
         <v>24.7</v>
       </c>
       <c r="M74">
-        <v>48.5919936</v>
+        <v>49.2668824</v>
       </c>
       <c r="N74">
-        <v>-23.8919936</v>
+        <v>-24.5668824</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-23.8919936</v>
+        <v>-24.5668824</v>
       </c>
       <c r="Q74">
-        <v>-16.8919936</v>
+        <v>-17.5668824</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4041452076579335</v>
+        <v>0.4174172523860051</v>
       </c>
       <c r="T74">
-        <v>3.069507548345496</v>
+        <v>3.183193013099033</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5083141927315368</v>
+        <v>0.5013509846119266</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2592866581442214</v>
+        <v>0.2867366581442214</v>
       </c>
       <c r="C75">
-        <v>-68.88476933657827</v>
+        <v>-92.0193208932665</v>
       </c>
       <c r="D75">
-        <v>173.5582306634217</v>
+        <v>153.7846791067335</v>
       </c>
       <c r="E75">
-        <v>184.953</v>
+        <v>188.314</v>
       </c>
       <c r="F75">
-        <v>245.353</v>
+        <v>248.714</v>
       </c>
       <c r="G75">
         <v>2.91</v>
@@ -7437,45 +7437,45 @@
         <v>24.7</v>
       </c>
       <c r="M75">
-        <v>49.2668824</v>
+        <v>58.64676119999999</v>
       </c>
       <c r="N75">
-        <v>-24.5668824</v>
+        <v>-33.9467612</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-24.5668824</v>
+        <v>-33.9467612</v>
       </c>
       <c r="Q75">
-        <v>-17.5668824</v>
+        <v>-26.9467612</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4174172523860051</v>
+        <v>0.4317102236316207</v>
       </c>
       <c r="T75">
-        <v>3.183193013099033</v>
+        <v>3.305623513602842</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5013509846119266</v>
+        <v>0.4211656278130496</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2867366581442214</v>
+        <v>0.2886366581442214</v>
       </c>
       <c r="C76">
-        <v>-92.0193208932665</v>
+        <v>-96.58356134524666</v>
       </c>
       <c r="D76">
-        <v>153.7846791067335</v>
+        <v>152.5814386547533</v>
       </c>
       <c r="E76">
-        <v>188.314</v>
+        <v>191.675</v>
       </c>
       <c r="F76">
-        <v>248.714</v>
+        <v>252.075</v>
       </c>
       <c r="G76">
         <v>2.91</v>
@@ -7519,28 +7519,28 @@
         <v>24.7</v>
       </c>
       <c r="M76">
-        <v>58.64676119999999</v>
+        <v>59.439285</v>
       </c>
       <c r="N76">
-        <v>-33.9467612</v>
+        <v>-34.739285</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-33.9467612</v>
+        <v>-34.739285</v>
       </c>
       <c r="Q76">
-        <v>-26.9467612</v>
+        <v>-27.739285</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4317102236316207</v>
+        <v>0.4471466325768856</v>
       </c>
       <c r="T76">
-        <v>3.305623513602842</v>
+        <v>3.437848454146956</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4211656278130496</v>
+        <v>0.4155500861088757</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2886366581442214</v>
+        <v>0.2905366581442214</v>
       </c>
       <c r="C77">
-        <v>-96.58356134524666</v>
+        <v>-101.1291192110045</v>
       </c>
       <c r="D77">
-        <v>152.5814386547533</v>
+        <v>151.3968807889955</v>
       </c>
       <c r="E77">
-        <v>191.675</v>
+        <v>195.036</v>
       </c>
       <c r="F77">
-        <v>252.075</v>
+        <v>255.436</v>
       </c>
       <c r="G77">
         <v>2.91</v>
@@ -7601,28 +7601,28 @@
         <v>24.7</v>
       </c>
       <c r="M77">
-        <v>59.439285</v>
+        <v>60.2318088</v>
       </c>
       <c r="N77">
-        <v>-34.739285</v>
+        <v>-35.53180879999999</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-34.739285</v>
+        <v>-35.53180879999999</v>
       </c>
       <c r="Q77">
-        <v>-27.739285</v>
+        <v>-28.53180879999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4471466325768856</v>
+        <v>0.4638694089342559</v>
       </c>
       <c r="T77">
-        <v>3.437848454146956</v>
+        <v>3.581092139736413</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4155500861088757</v>
+        <v>0.4100823218179694</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2905366581442214</v>
+        <v>0.2924366581442214</v>
       </c>
       <c r="C78">
-        <v>-101.1291192110045</v>
+        <v>-105.65642626229</v>
       </c>
       <c r="D78">
-        <v>151.3968807889955</v>
+        <v>150.23057373771</v>
       </c>
       <c r="E78">
-        <v>195.036</v>
+        <v>198.397</v>
       </c>
       <c r="F78">
-        <v>255.436</v>
+        <v>258.797</v>
       </c>
       <c r="G78">
         <v>2.91</v>
@@ -7683,28 +7683,28 @@
         <v>24.7</v>
       </c>
       <c r="M78">
-        <v>60.2318088</v>
+        <v>61.02433259999999</v>
       </c>
       <c r="N78">
-        <v>-35.53180879999999</v>
+        <v>-36.32433259999999</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-35.53180879999999</v>
+        <v>-36.32433259999999</v>
       </c>
       <c r="Q78">
-        <v>-28.53180879999999</v>
+        <v>-29.32433259999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4638694089342559</v>
+        <v>0.4820463397574843</v>
       </c>
       <c r="T78">
-        <v>3.581092139736413</v>
+        <v>3.736791797985822</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4100823218179694</v>
+        <v>0.404756577378775</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2924366581442214</v>
+        <v>0.2943366581442214</v>
       </c>
       <c r="C79">
-        <v>-105.65642626229</v>
+        <v>-110.1659010677089</v>
       </c>
       <c r="D79">
-        <v>150.23057373771</v>
+        <v>149.0820989322911</v>
       </c>
       <c r="E79">
-        <v>198.397</v>
+        <v>201.758</v>
       </c>
       <c r="F79">
-        <v>258.797</v>
+        <v>262.158</v>
       </c>
       <c r="G79">
         <v>2.91</v>
@@ -7765,28 +7765,28 @@
         <v>24.7</v>
       </c>
       <c r="M79">
-        <v>61.02433259999999</v>
+        <v>61.81685639999999</v>
       </c>
       <c r="N79">
-        <v>-36.32433259999999</v>
+        <v>-37.11685639999999</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-36.32433259999999</v>
+        <v>-37.11685639999999</v>
       </c>
       <c r="Q79">
-        <v>-29.32433259999999</v>
+        <v>-30.11685639999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4820463397574843</v>
+        <v>0.50187571883737</v>
       </c>
       <c r="T79">
-        <v>3.736791797985822</v>
+        <v>3.906645970621542</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.404756577378775</v>
+        <v>0.3995673904893036</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2943366581442214</v>
+        <v>0.2962366581442214</v>
       </c>
       <c r="C80">
-        <v>-110.1659010677089</v>
+        <v>-114.6579494935677</v>
       </c>
       <c r="D80">
-        <v>149.0820989322911</v>
+        <v>147.9510505064323</v>
       </c>
       <c r="E80">
-        <v>201.758</v>
+        <v>205.119</v>
       </c>
       <c r="F80">
-        <v>262.158</v>
+        <v>265.519</v>
       </c>
       <c r="G80">
         <v>2.91</v>
@@ -7847,28 +7847,28 @@
         <v>24.7</v>
       </c>
       <c r="M80">
-        <v>61.81685639999999</v>
+        <v>62.6093802</v>
       </c>
       <c r="N80">
-        <v>-37.11685639999999</v>
+        <v>-37.9093802</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-37.11685639999999</v>
+        <v>-37.9093802</v>
       </c>
       <c r="Q80">
-        <v>-30.11685639999999</v>
+        <v>-30.9093802</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.50187571883737</v>
+        <v>0.5235936102105782</v>
       </c>
       <c r="T80">
-        <v>3.906645970621542</v>
+        <v>4.092676731127329</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3995673904893036</v>
+        <v>0.3945095754198187</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2962366581442214</v>
+        <v>0.2981366581442214</v>
       </c>
       <c r="C81">
-        <v>-114.6579494935677</v>
+        <v>-119.1329651820911</v>
       </c>
       <c r="D81">
-        <v>147.9510505064323</v>
+        <v>146.8370348179089</v>
       </c>
       <c r="E81">
-        <v>205.119</v>
+        <v>208.48</v>
       </c>
       <c r="F81">
-        <v>265.519</v>
+        <v>268.88</v>
       </c>
       <c r="G81">
         <v>2.91</v>
@@ -7929,28 +7929,28 @@
         <v>24.7</v>
       </c>
       <c r="M81">
-        <v>62.6093802</v>
+        <v>63.401904</v>
       </c>
       <c r="N81">
-        <v>-37.9093802</v>
+        <v>-38.701904</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-37.9093802</v>
+        <v>-38.701904</v>
       </c>
       <c r="Q81">
-        <v>-30.9093802</v>
+        <v>-31.701904</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5235936102105782</v>
+        <v>0.547483290721107</v>
       </c>
       <c r="T81">
-        <v>4.092676731127329</v>
+        <v>4.297310567683696</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3945095754198187</v>
+        <v>0.3895782057270709</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2981366581442214</v>
+        <v>0.3000366581442214</v>
       </c>
       <c r="C82">
-        <v>-119.1329651820911</v>
+        <v>-123.5913300081964</v>
       </c>
       <c r="D82">
-        <v>146.8370348179089</v>
+        <v>145.7396699918036</v>
       </c>
       <c r="E82">
-        <v>208.48</v>
+        <v>211.841</v>
       </c>
       <c r="F82">
-        <v>268.88</v>
+        <v>272.241</v>
       </c>
       <c r="G82">
         <v>2.91</v>
@@ -8011,28 +8011,28 @@
         <v>24.7</v>
       </c>
       <c r="M82">
-        <v>63.401904</v>
+        <v>64.1944278</v>
       </c>
       <c r="N82">
-        <v>-38.701904</v>
+        <v>-39.4944278</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-38.701904</v>
+        <v>-39.4944278</v>
       </c>
       <c r="Q82">
-        <v>-31.701904</v>
+        <v>-32.4944278</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.547483290721107</v>
+        <v>0.5738876744432706</v>
       </c>
       <c r="T82">
-        <v>4.297310567683696</v>
+        <v>4.523484808088101</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3895782057270709</v>
+        <v>0.3847685982489589</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3000366581442214</v>
+        <v>0.3019366581442214</v>
       </c>
       <c r="C83">
-        <v>-123.5913300081964</v>
+        <v>-128.033414515938</v>
       </c>
       <c r="D83">
-        <v>145.7396699918036</v>
+        <v>144.658585484062</v>
       </c>
       <c r="E83">
-        <v>211.841</v>
+        <v>215.202</v>
       </c>
       <c r="F83">
-        <v>272.241</v>
+        <v>275.602</v>
       </c>
       <c r="G83">
         <v>2.91</v>
@@ -8093,28 +8093,28 @@
         <v>24.7</v>
       </c>
       <c r="M83">
-        <v>64.1944278</v>
+        <v>64.9869516</v>
       </c>
       <c r="N83">
-        <v>-39.4944278</v>
+        <v>-40.28695159999999</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-39.4944278</v>
+        <v>-40.28695159999999</v>
       </c>
       <c r="Q83">
-        <v>-32.4944278</v>
+        <v>-33.28695159999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5738876744432706</v>
+        <v>0.6032258785790079</v>
       </c>
       <c r="T83">
-        <v>4.523484808088101</v>
+        <v>4.774789519648552</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3847685982489589</v>
+        <v>0.3800762982703132</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3019366581442214</v>
+        <v>0.3038366581442214</v>
       </c>
       <c r="C84">
-        <v>-128.033414515938</v>
+        <v>-132.4595783356698</v>
       </c>
       <c r="D84">
-        <v>144.658585484062</v>
+        <v>143.5934216643302</v>
       </c>
       <c r="E84">
-        <v>215.202</v>
+        <v>218.563</v>
       </c>
       <c r="F84">
-        <v>275.602</v>
+        <v>278.963</v>
       </c>
       <c r="G84">
         <v>2.91</v>
@@ -8175,28 +8175,28 @@
         <v>24.7</v>
       </c>
       <c r="M84">
-        <v>64.9869516</v>
+        <v>65.77947540000001</v>
       </c>
       <c r="N84">
-        <v>-40.28695159999999</v>
+        <v>-41.07947540000001</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-40.28695159999999</v>
+        <v>-41.07947540000001</v>
       </c>
       <c r="Q84">
-        <v>-33.28695159999999</v>
+        <v>-34.07947540000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6032258785790079</v>
+        <v>0.636015636142479</v>
       </c>
       <c r="T84">
-        <v>4.774789519648552</v>
+        <v>5.055659491392585</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3800762982703132</v>
+        <v>0.3754970657610321</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3038366581442214</v>
+        <v>0.3057366581442215</v>
       </c>
       <c r="C85">
-        <v>-132.4595783356698</v>
+        <v>-136.870170582912</v>
       </c>
       <c r="D85">
-        <v>143.5934216643302</v>
+        <v>142.543829417088</v>
       </c>
       <c r="E85">
-        <v>218.563</v>
+        <v>221.924</v>
       </c>
       <c r="F85">
-        <v>278.963</v>
+        <v>282.324</v>
       </c>
       <c r="G85">
         <v>2.91</v>
@@ -8257,28 +8257,28 @@
         <v>24.7</v>
       </c>
       <c r="M85">
-        <v>65.77947540000001</v>
+        <v>66.57199920000001</v>
       </c>
       <c r="N85">
-        <v>-41.07947540000001</v>
+        <v>-41.8719992</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-41.07947540000001</v>
+        <v>-41.8719992</v>
       </c>
       <c r="Q85">
-        <v>-34.07947540000001</v>
+        <v>-34.8719992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.636015636142479</v>
+        <v>0.6729041134013841</v>
       </c>
       <c r="T85">
-        <v>5.055659491392585</v>
+        <v>5.371638209604622</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3754970657610321</v>
+        <v>0.3710268625972104</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3057366581442214</v>
+        <v>0.3076366581442214</v>
       </c>
       <c r="C86">
-        <v>-136.8701705829119</v>
+        <v>-141.2655302398523</v>
       </c>
       <c r="D86">
-        <v>142.5438294170881</v>
+        <v>141.5094697601477</v>
       </c>
       <c r="E86">
-        <v>221.9239999999999</v>
+        <v>225.2849999999999</v>
       </c>
       <c r="F86">
-        <v>282.324</v>
+        <v>285.6849999999999</v>
       </c>
       <c r="G86">
         <v>2.91</v>
@@ -8339,28 +8339,28 @@
         <v>24.7</v>
       </c>
       <c r="M86">
-        <v>66.57199919999999</v>
+        <v>67.36452299999999</v>
       </c>
       <c r="N86">
-        <v>-41.87199919999999</v>
+        <v>-42.66452299999999</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-41.87199919999999</v>
+        <v>-42.66452299999999</v>
       </c>
       <c r="Q86">
-        <v>-34.87199919999999</v>
+        <v>-35.66452299999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6729041134013836</v>
+        <v>0.7147110542948092</v>
       </c>
       <c r="T86">
-        <v>5.371638209604618</v>
+        <v>5.72974742357826</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3710268625972105</v>
+        <v>0.3666618406843021</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3076366581442214</v>
+        <v>0.3095366581442214</v>
       </c>
       <c r="C87">
-        <v>-141.2655302398523</v>
+        <v>-145.6459865203564</v>
       </c>
       <c r="D87">
-        <v>141.5094697601477</v>
+        <v>140.4900134796436</v>
       </c>
       <c r="E87">
-        <v>225.2849999999999</v>
+        <v>228.646</v>
       </c>
       <c r="F87">
-        <v>285.6849999999999</v>
+        <v>289.046</v>
       </c>
       <c r="G87">
         <v>2.91</v>
@@ -8421,28 +8421,28 @@
         <v>24.7</v>
       </c>
       <c r="M87">
-        <v>67.36452299999999</v>
+        <v>68.1570468</v>
       </c>
       <c r="N87">
-        <v>-42.66452299999999</v>
+        <v>-43.4570468</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-42.66452299999999</v>
+        <v>-43.4570468</v>
       </c>
       <c r="Q87">
-        <v>-35.66452299999999</v>
+        <v>-36.4570468</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7147110542948092</v>
+        <v>0.762490415315867</v>
       </c>
       <c r="T87">
-        <v>5.72974742357826</v>
+        <v>6.139015096690993</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3666618406843021</v>
+        <v>0.3623983309089032</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3095366581442214</v>
+        <v>0.3114366581442214</v>
       </c>
       <c r="C88">
-        <v>-145.6459865203564</v>
+        <v>-150.0118592193134</v>
       </c>
       <c r="D88">
-        <v>140.4900134796436</v>
+        <v>139.4851407806866</v>
       </c>
       <c r="E88">
-        <v>228.646</v>
+        <v>232.007</v>
       </c>
       <c r="F88">
-        <v>289.046</v>
+        <v>292.407</v>
       </c>
       <c r="G88">
         <v>2.91</v>
@@ -8503,28 +8503,28 @@
         <v>24.7</v>
       </c>
       <c r="M88">
-        <v>68.1570468</v>
+        <v>68.9495706</v>
       </c>
       <c r="N88">
-        <v>-43.4570468</v>
+        <v>-44.2495706</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-43.4570468</v>
+        <v>-44.2495706</v>
       </c>
       <c r="Q88">
-        <v>-36.4570468</v>
+        <v>-37.2495706</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.762490415315867</v>
+        <v>0.8176204472632413</v>
       </c>
       <c r="T88">
-        <v>6.139015096690993</v>
+        <v>6.611247027205684</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3623983309089032</v>
+        <v>0.358232832852479</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3114366581442214</v>
+        <v>0.3133366581442214</v>
       </c>
       <c r="C89">
-        <v>-150.0118592193134</v>
+        <v>-154.3634590470964</v>
       </c>
       <c r="D89">
-        <v>139.4851407806866</v>
+        <v>138.4945409529035</v>
       </c>
       <c r="E89">
-        <v>232.007</v>
+        <v>235.368</v>
       </c>
       <c r="F89">
-        <v>292.407</v>
+        <v>295.768</v>
       </c>
       <c r="G89">
         <v>2.91</v>
@@ -8585,28 +8585,28 @@
         <v>24.7</v>
       </c>
       <c r="M89">
-        <v>68.9495706</v>
+        <v>69.7420944</v>
       </c>
       <c r="N89">
-        <v>-44.2495706</v>
+        <v>-45.0420944</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-44.2495706</v>
+        <v>-45.0420944</v>
       </c>
       <c r="Q89">
-        <v>-37.2495706</v>
+        <v>-38.0420944</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8176204472632413</v>
+        <v>0.8819388178685117</v>
       </c>
       <c r="T89">
-        <v>6.611247027205684</v>
+        <v>7.162184279472826</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.358232832852479</v>
+        <v>0.3541620052064282</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3133366581442214</v>
+        <v>0.3152366581442214</v>
       </c>
       <c r="C90">
-        <v>-154.3634590470964</v>
+        <v>-158.7010879498705</v>
       </c>
       <c r="D90">
-        <v>138.4945409529035</v>
+        <v>137.5179120501294</v>
       </c>
       <c r="E90">
-        <v>235.368</v>
+        <v>238.729</v>
       </c>
       <c r="F90">
-        <v>295.768</v>
+        <v>299.129</v>
       </c>
       <c r="G90">
         <v>2.91</v>
@@ -8667,28 +8667,28 @@
         <v>24.7</v>
       </c>
       <c r="M90">
-        <v>69.7420944</v>
+        <v>70.5346182</v>
       </c>
       <c r="N90">
-        <v>-45.0420944</v>
+        <v>-45.83461819999999</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-45.0420944</v>
+        <v>-45.83461819999999</v>
       </c>
       <c r="Q90">
-        <v>-38.0420944</v>
+        <v>-38.83461819999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8819388178685117</v>
+        <v>0.95795143767474</v>
       </c>
       <c r="T90">
-        <v>7.162184279472826</v>
+        <v>7.813291941243083</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3541620052064282</v>
+        <v>0.3501826568333222</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3152366581442214</v>
+        <v>0.3171366581442214</v>
       </c>
       <c r="C91">
-        <v>-158.7010879498705</v>
+        <v>-163.0250394164445</v>
       </c>
       <c r="D91">
-        <v>137.5179120501294</v>
+        <v>136.5549605835555</v>
       </c>
       <c r="E91">
-        <v>238.729</v>
+        <v>242.0899999999999</v>
       </c>
       <c r="F91">
-        <v>299.129</v>
+        <v>302.49</v>
       </c>
       <c r="G91">
         <v>2.91</v>
@@ -8749,28 +8749,28 @@
         <v>24.7</v>
       </c>
       <c r="M91">
-        <v>70.5346182</v>
+        <v>71.32714199999999</v>
       </c>
       <c r="N91">
-        <v>-45.83461819999999</v>
+        <v>-46.62714199999999</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-45.83461819999999</v>
+        <v>-46.62714199999999</v>
       </c>
       <c r="Q91">
-        <v>-38.83461819999999</v>
+        <v>-39.62714199999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.95795143767474</v>
+        <v>1.049166581442214</v>
       </c>
       <c r="T91">
-        <v>7.813291941243083</v>
+        <v>8.594621135367392</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3501826568333222</v>
+        <v>0.3462917384240631</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3171366581442214</v>
+        <v>0.3190366581442214</v>
       </c>
       <c r="C92">
-        <v>-163.0250394164445</v>
+        <v>-167.3355987723191</v>
       </c>
       <c r="D92">
-        <v>136.5549605835555</v>
+        <v>135.6054012276809</v>
       </c>
       <c r="E92">
-        <v>242.0899999999999</v>
+        <v>245.451</v>
       </c>
       <c r="F92">
-        <v>302.49</v>
+        <v>305.851</v>
       </c>
       <c r="G92">
         <v>2.91</v>
@@ -8831,28 +8831,28 @@
         <v>24.7</v>
       </c>
       <c r="M92">
-        <v>71.32714199999999</v>
+        <v>72.11966580000001</v>
       </c>
       <c r="N92">
-        <v>-46.62714199999999</v>
+        <v>-47.4196658</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-46.62714199999999</v>
+        <v>-47.4196658</v>
       </c>
       <c r="Q92">
-        <v>-39.62714199999999</v>
+        <v>-40.4196658</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.049166581442214</v>
+        <v>1.160651757158016</v>
       </c>
       <c r="T92">
-        <v>8.594621135367392</v>
+        <v>9.549579039297104</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3462917384240631</v>
+        <v>0.3424863347051172</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3190366581442214</v>
+        <v>0.3209366581442215</v>
       </c>
       <c r="C93">
-        <v>-167.3355987723191</v>
+        <v>-171.6330434615526</v>
       </c>
       <c r="D93">
-        <v>135.6054012276809</v>
+        <v>134.6689565384474</v>
       </c>
       <c r="E93">
-        <v>245.451</v>
+        <v>248.812</v>
       </c>
       <c r="F93">
-        <v>305.851</v>
+        <v>309.212</v>
       </c>
       <c r="G93">
         <v>2.91</v>
@@ -8913,28 +8913,28 @@
         <v>24.7</v>
       </c>
       <c r="M93">
-        <v>72.11966580000001</v>
+        <v>72.9121896</v>
       </c>
       <c r="N93">
-        <v>-47.4196658</v>
+        <v>-48.2121896</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-47.4196658</v>
+        <v>-48.2121896</v>
       </c>
       <c r="Q93">
-        <v>-40.4196658</v>
+        <v>-41.2121896</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.160651757158016</v>
+        <v>1.300008226802768</v>
       </c>
       <c r="T93">
-        <v>9.549579039297104</v>
+        <v>10.74327641920924</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3424863347051172</v>
+        <v>0.3387636571539747</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3209366581442215</v>
+        <v>0.3228366581442214</v>
       </c>
       <c r="C94">
-        <v>-171.6330434615526</v>
+        <v>-175.9176433170267</v>
       </c>
       <c r="D94">
-        <v>134.6689565384474</v>
+        <v>133.7453566829733</v>
       </c>
       <c r="E94">
-        <v>248.812</v>
+        <v>252.173</v>
       </c>
       <c r="F94">
-        <v>309.212</v>
+        <v>312.573</v>
       </c>
       <c r="G94">
         <v>2.91</v>
@@ -8995,28 +8995,28 @@
         <v>24.7</v>
       </c>
       <c r="M94">
-        <v>72.9121896</v>
+        <v>73.7047134</v>
       </c>
       <c r="N94">
-        <v>-48.2121896</v>
+        <v>-49.0047134</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-48.2121896</v>
+        <v>-49.0047134</v>
       </c>
       <c r="Q94">
-        <v>-41.2121896</v>
+        <v>-42.0047134</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.300008226802768</v>
+        <v>1.479180830631735</v>
       </c>
       <c r="T94">
-        <v>10.74327641920924</v>
+        <v>12.27803019338199</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3387636571539747</v>
+        <v>0.3351210371845772</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3228366581442214</v>
+        <v>0.3247366581442214</v>
       </c>
       <c r="C95">
-        <v>-175.9176433170267</v>
+        <v>-180.189660819668</v>
       </c>
       <c r="D95">
-        <v>133.7453566829733</v>
+        <v>132.834339180332</v>
       </c>
       <c r="E95">
-        <v>252.173</v>
+        <v>255.534</v>
       </c>
       <c r="F95">
-        <v>312.573</v>
+        <v>315.934</v>
       </c>
       <c r="G95">
         <v>2.91</v>
@@ -9077,28 +9077,28 @@
         <v>24.7</v>
       </c>
       <c r="M95">
-        <v>73.7047134</v>
+        <v>74.4972372</v>
       </c>
       <c r="N95">
-        <v>-49.0047134</v>
+        <v>-49.7972372</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-49.0047134</v>
+        <v>-49.7972372</v>
       </c>
       <c r="Q95">
-        <v>-42.0047134</v>
+        <v>-42.7972372</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.479180830631735</v>
+        <v>1.718077635737025</v>
       </c>
       <c r="T95">
-        <v>12.27803019338199</v>
+        <v>14.32436855894566</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3351210371845772</v>
+        <v>0.3315559197677199</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3247366581442214</v>
+        <v>0.3266366581442214</v>
       </c>
       <c r="C96">
-        <v>-180.189660819668</v>
+        <v>-184.4493513471455</v>
       </c>
       <c r="D96">
-        <v>132.834339180332</v>
+        <v>131.9356486528546</v>
       </c>
       <c r="E96">
-        <v>255.534</v>
+        <v>258.895</v>
       </c>
       <c r="F96">
-        <v>315.934</v>
+        <v>319.295</v>
       </c>
       <c r="G96">
         <v>2.91</v>
@@ -9159,28 +9159,28 @@
         <v>24.7</v>
       </c>
       <c r="M96">
-        <v>74.4972372</v>
+        <v>75.28976100000001</v>
       </c>
       <c r="N96">
-        <v>-49.7972372</v>
+        <v>-50.58976100000001</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-49.7972372</v>
+        <v>-50.58976100000001</v>
       </c>
       <c r="Q96">
-        <v>-42.7972372</v>
+        <v>-43.58976100000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.718077635737025</v>
+        <v>2.052533162884431</v>
       </c>
       <c r="T96">
-        <v>14.32436855894566</v>
+        <v>17.18924227073481</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3315559197677199</v>
+        <v>0.3280658574543754</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3266366581442214</v>
+        <v>0.3285366581442214</v>
       </c>
       <c r="C97">
-        <v>-184.4493513471455</v>
+        <v>-188.6969634125415</v>
       </c>
       <c r="D97">
-        <v>131.9356486528546</v>
+        <v>131.0490365874585</v>
       </c>
       <c r="E97">
-        <v>258.895</v>
+        <v>262.256</v>
       </c>
       <c r="F97">
-        <v>319.295</v>
+        <v>322.656</v>
       </c>
       <c r="G97">
         <v>2.91</v>
@@ -9241,28 +9241,28 @@
         <v>24.7</v>
       </c>
       <c r="M97">
-        <v>75.28976100000001</v>
+        <v>76.08228480000001</v>
       </c>
       <c r="N97">
-        <v>-50.58976100000001</v>
+        <v>-51.38228480000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-50.58976100000001</v>
+        <v>-51.38228480000001</v>
       </c>
       <c r="Q97">
-        <v>-43.58976100000001</v>
+        <v>-44.38228480000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.052533162884431</v>
+        <v>2.554216453605539</v>
       </c>
       <c r="T97">
-        <v>17.18924227073481</v>
+        <v>21.48655283841851</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3280658574543754</v>
+        <v>0.3246485047725591</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3285366581442214</v>
+        <v>0.3304366581442214</v>
       </c>
       <c r="C98">
-        <v>-188.6969634125414</v>
+        <v>-192.9327388934635</v>
       </c>
       <c r="D98">
-        <v>131.0490365874585</v>
+        <v>130.1742611065364</v>
       </c>
       <c r="E98">
-        <v>262.256</v>
+        <v>265.617</v>
       </c>
       <c r="F98">
-        <v>322.6559999999999</v>
+        <v>326.0169999999999</v>
       </c>
       <c r="G98">
         <v>2.91</v>
@@ -9323,28 +9323,28 @@
         <v>24.7</v>
       </c>
       <c r="M98">
-        <v>76.0822848</v>
+        <v>76.87480859999999</v>
       </c>
       <c r="N98">
-        <v>-51.38228479999999</v>
+        <v>-52.17480859999999</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-51.38228479999999</v>
+        <v>-52.17480859999999</v>
       </c>
       <c r="Q98">
-        <v>-44.38228479999999</v>
+        <v>-45.17480859999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.554216453605533</v>
+        <v>3.390355271474044</v>
       </c>
       <c r="T98">
-        <v>21.48655283841846</v>
+        <v>28.64873711789128</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3246485047725591</v>
+        <v>0.3213016129707802</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3304366581442214</v>
+        <v>0.3323366581442214</v>
       </c>
       <c r="C99">
-        <v>-192.9327388934635</v>
+        <v>-197.1569132520405</v>
       </c>
       <c r="D99">
-        <v>130.1742611065364</v>
+        <v>129.3110867479595</v>
       </c>
       <c r="E99">
-        <v>265.617</v>
+        <v>268.978</v>
       </c>
       <c r="F99">
-        <v>326.0169999999999</v>
+        <v>329.378</v>
       </c>
       <c r="G99">
         <v>2.91</v>
@@ -9405,28 +9405,28 @@
         <v>24.7</v>
       </c>
       <c r="M99">
-        <v>76.87480859999999</v>
+        <v>77.66733240000001</v>
       </c>
       <c r="N99">
-        <v>-52.17480859999999</v>
+        <v>-52.9673324</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-52.17480859999999</v>
+        <v>-52.9673324</v>
       </c>
       <c r="Q99">
-        <v>-45.17480859999999</v>
+        <v>-45.9673324</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.390355271474044</v>
+        <v>5.062632907211065</v>
       </c>
       <c r="T99">
-        <v>28.64873711789128</v>
+        <v>42.97310567683692</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3213016129707802</v>
+        <v>0.3180230250833233</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3323366581442214</v>
+        <v>0.3342366581442214</v>
       </c>
       <c r="C100">
-        <v>-197.1569132520405</v>
+        <v>-201.3697157462237</v>
       </c>
       <c r="D100">
-        <v>129.3110867479595</v>
+        <v>128.4592842537762</v>
       </c>
       <c r="E100">
-        <v>268.978</v>
+        <v>272.339</v>
       </c>
       <c r="F100">
-        <v>329.378</v>
+        <v>332.739</v>
       </c>
       <c r="G100">
         <v>2.91</v>
@@ -9487,28 +9487,28 @@
         <v>24.7</v>
       </c>
       <c r="M100">
-        <v>77.66733240000001</v>
+        <v>78.4598562</v>
       </c>
       <c r="N100">
-        <v>-52.9673324</v>
+        <v>-53.7598562</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-52.9673324</v>
+        <v>-53.7598562</v>
       </c>
       <c r="Q100">
-        <v>-45.9673324</v>
+        <v>-46.7598562</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.062632907211065</v>
+        <v>10.07946581442213</v>
       </c>
       <c r="T100">
-        <v>42.97310567683692</v>
+        <v>85.94621135367383</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3180230250833233</v>
+        <v>0.3148106712946028</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3342366581442214</v>
-      </c>
-      <c r="C101">
-        <v>-201.3697157462237</v>
-      </c>
-      <c r="D101">
-        <v>128.4592842537762</v>
-      </c>
-      <c r="E101">
-        <v>272.339</v>
-      </c>
-      <c r="F101">
-        <v>332.739</v>
-      </c>
-      <c r="G101">
-        <v>2.91</v>
-      </c>
-      <c r="H101">
-        <v>275.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.7</v>
-      </c>
-      <c r="K101">
-        <v>7</v>
-      </c>
-      <c r="L101">
-        <v>24.7</v>
-      </c>
-      <c r="M101">
-        <v>78.4598562</v>
-      </c>
-      <c r="N101">
-        <v>-53.7598562</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-53.7598562</v>
-      </c>
-      <c r="Q101">
-        <v>-46.7598562</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.07946581442213</v>
-      </c>
-      <c r="T101">
-        <v>85.94621135367383</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3148106712946028</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
